--- a/Do Not Touch/details_of_strains_isolates_clones.xlsx
+++ b/Do Not Touch/details_of_strains_isolates_clones.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victoriamedina/Thesis_Project/Thesis/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/victoriamedina/Thesis_Project/Thesis/Do Not Touch/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5C6523-57C9-724A-86DE-F7310BE70413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D01F21-F588-E242-9BC9-6AF002AE0D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14620" yWindow="760" windowWidth="15100" windowHeight="17120" xr2:uid="{E90AC6F4-0D19-024A-819D-31B9E4B9AA5D}"/>
+    <workbookView xWindow="800" yWindow="880" windowWidth="29060" windowHeight="17120" xr2:uid="{E90AC6F4-0D19-024A-819D-31B9E4B9AA5D}"/>
   </bookViews>
   <sheets>
     <sheet name="Cleaned_Description_Counts" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2696" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="551">
   <si>
     <t>Description Type</t>
   </si>
@@ -1674,6 +1674,18 @@
   </si>
   <si>
     <t>AK022D-0</t>
+  </si>
+  <si>
+    <t>3D7 K1</t>
+  </si>
+  <si>
+    <t>Delete: Not specified</t>
+  </si>
+  <si>
+    <t>D10 7G8</t>
+  </si>
+  <si>
+    <t>If D10 comes first then pick it, and vice versa</t>
   </si>
 </sst>
 </file>
@@ -2580,7 +2592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A103CF64-ACD7-6049-A739-5D9831EFD197}">
-  <dimension ref="A1:O498"/>
+  <dimension ref="A1:O499"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.5" customWidth="1"/>
@@ -2947,30 +2959,33 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B18">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D18" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F18" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>398</v>
+      </c>
+      <c r="H18" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B19">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D19" t="s">
         <v>396</v>
@@ -2983,17 +2998,14 @@
       </c>
       <c r="G19" t="s">
         <v>398</v>
-      </c>
-      <c r="H19" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B20">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D20" t="s">
         <v>396</v>
@@ -3010,10 +3022,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B21">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="D21" t="s">
         <v>396</v>
@@ -3026,14 +3038,17 @@
       </c>
       <c r="G21" t="s">
         <v>398</v>
+      </c>
+      <c r="H21" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B22">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="D22" t="s">
         <v>396</v>
@@ -3046,17 +3061,14 @@
       </c>
       <c r="G22" t="s">
         <v>398</v>
-      </c>
-      <c r="H22" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B23">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="D23" t="s">
         <v>396</v>
@@ -3073,10 +3085,10 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B24">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D24" t="s">
         <v>396</v>
@@ -3093,10 +3105,10 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B25">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D25" t="s">
         <v>396</v>
@@ -3113,30 +3125,33 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B26">
+        <v>87</v>
+      </c>
+      <c r="D26" t="s">
+        <v>396</v>
+      </c>
+      <c r="E26" t="s">
+        <v>398</v>
+      </c>
+      <c r="F26" t="s">
+        <v>398</v>
+      </c>
+      <c r="G26" t="s">
+        <v>398</v>
+      </c>
+      <c r="H26" t="s">
         <v>26</v>
-      </c>
-      <c r="B26">
-        <v>90</v>
-      </c>
-      <c r="D26" t="s">
-        <v>396</v>
-      </c>
-      <c r="E26" t="s">
-        <v>398</v>
-      </c>
-      <c r="F26" t="s">
-        <v>398</v>
-      </c>
-      <c r="G26" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B27">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="D27" t="s">
         <v>396</v>
@@ -3149,17 +3164,14 @@
       </c>
       <c r="G27" t="s">
         <v>398</v>
-      </c>
-      <c r="H27" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B28">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
         <v>396</v>
@@ -3176,7 +3188,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B29">
         <v>59</v>
@@ -3196,53 +3208,53 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B30">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E30" t="s">
         <v>398</v>
       </c>
       <c r="F30" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G30" t="s">
         <v>398</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D31" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E31" t="s">
         <v>398</v>
       </c>
       <c r="F31" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G31" t="s">
         <v>398</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D32" t="s">
         <v>396</v>
@@ -3259,10 +3271,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B33">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D33" t="s">
         <v>396</v>
@@ -3279,10 +3291,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B34">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D34" t="s">
         <v>396</v>
@@ -3295,11 +3307,14 @@
       </c>
       <c r="G34" t="s">
         <v>398</v>
+      </c>
+      <c r="H34" t="s">
+        <v>439</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B35">
         <v>49</v>
@@ -3316,16 +3331,13 @@
       <c r="G35" t="s">
         <v>398</v>
       </c>
-      <c r="H35" t="s">
-        <v>439</v>
-      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>237</v>
       </c>
       <c r="B36">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D36" t="s">
         <v>396</v>
@@ -3342,10 +3354,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>237</v>
+        <v>38</v>
       </c>
       <c r="B37">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D37" t="s">
         <v>396</v>
@@ -3362,10 +3374,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D38" t="s">
         <v>396</v>
@@ -3382,10 +3394,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D39" t="s">
         <v>396</v>
@@ -3398,14 +3410,17 @@
       </c>
       <c r="G39" t="s">
         <v>398</v>
+      </c>
+      <c r="H39" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
         <v>396</v>
@@ -3418,17 +3433,14 @@
       </c>
       <c r="G40" t="s">
         <v>398</v>
-      </c>
-      <c r="H40" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D41" t="s">
         <v>396</v>
@@ -3445,7 +3457,7 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B42">
         <v>37</v>
@@ -3465,10 +3477,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B43">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D43" t="s">
         <v>396</v>
@@ -3481,11 +3493,14 @@
       </c>
       <c r="G43" t="s">
         <v>398</v>
+      </c>
+      <c r="H43" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44">
         <v>35</v>
@@ -3502,13 +3517,10 @@
       <c r="G44" t="s">
         <v>398</v>
       </c>
-      <c r="H44" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45">
         <v>35</v>
@@ -3528,10 +3540,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>45</v>
+        <v>436</v>
       </c>
       <c r="B46">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D46" t="s">
         <v>396</v>
@@ -3548,10 +3560,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>436</v>
+        <v>46</v>
       </c>
       <c r="B47">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D47" t="s">
         <v>396</v>
@@ -3568,7 +3580,7 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B48">
         <v>33</v>
@@ -3588,7 +3600,7 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49">
         <v>33</v>
@@ -3608,10 +3620,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B50">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D50" t="s">
         <v>396</v>
@@ -3628,7 +3640,7 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51">
         <v>32</v>
@@ -3648,10 +3660,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B52">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D52" t="s">
         <v>396</v>
@@ -3668,10 +3680,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B53">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D53" t="s">
         <v>396</v>
@@ -3688,7 +3700,7 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B54">
         <v>26</v>
@@ -3705,10 +3717,13 @@
       <c r="G54" t="s">
         <v>398</v>
       </c>
+      <c r="H54" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55">
         <v>26</v>
@@ -3726,12 +3741,12 @@
         <v>398</v>
       </c>
       <c r="H55" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B56">
         <v>26</v>
@@ -3749,12 +3764,12 @@
         <v>398</v>
       </c>
       <c r="H56" t="s">
-        <v>5</v>
+        <v>438</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B57">
         <v>26</v>
@@ -3771,16 +3786,13 @@
       <c r="G57" t="s">
         <v>398</v>
       </c>
-      <c r="H57" t="s">
-        <v>438</v>
-      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B58">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D58" t="s">
         <v>396</v>
@@ -3797,10 +3809,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B59">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D59" t="s">
         <v>396</v>
@@ -3813,14 +3825,17 @@
       </c>
       <c r="G59" t="s">
         <v>398</v>
+      </c>
+      <c r="H59" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B60">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D60" t="s">
         <v>396</v>
@@ -3833,14 +3848,11 @@
       </c>
       <c r="G60" t="s">
         <v>398</v>
-      </c>
-      <c r="H60" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61">
         <v>23</v>
@@ -3860,7 +3872,7 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B62">
         <v>23</v>
@@ -3880,10 +3892,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B63">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D63" t="s">
         <v>396</v>
@@ -3896,11 +3908,14 @@
       </c>
       <c r="G63" t="s">
         <v>398</v>
+      </c>
+      <c r="H63" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B64">
         <v>22</v>
@@ -3917,13 +3932,10 @@
       <c r="G64" t="s">
         <v>398</v>
       </c>
-      <c r="H64" t="s">
-        <v>56</v>
-      </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B65">
         <v>22</v>
@@ -3943,10 +3955,10 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B66">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D66" t="s">
         <v>396</v>
@@ -3963,7 +3975,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B67">
         <v>20</v>
@@ -3983,10 +3995,10 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B68">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D68" t="s">
         <v>396</v>
@@ -3999,14 +4011,17 @@
       </c>
       <c r="G68" t="s">
         <v>398</v>
+      </c>
+      <c r="H68" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B69">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D69" t="s">
         <v>396</v>
@@ -4021,12 +4036,12 @@
         <v>398</v>
       </c>
       <c r="H69" t="s">
-        <v>34</v>
+        <v>442</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B70">
         <v>18</v>
@@ -4042,57 +4057,54 @@
       </c>
       <c r="G70" t="s">
         <v>398</v>
-      </c>
-      <c r="H70" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>69</v>
+        <v>444</v>
       </c>
       <c r="B71">
         <v>18</v>
       </c>
       <c r="D71" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E71" t="s">
         <v>398</v>
       </c>
       <c r="F71" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G71" t="s">
         <v>398</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>443</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>444</v>
+        <v>70</v>
       </c>
       <c r="B72">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D72" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E72" t="s">
         <v>398</v>
       </c>
       <c r="F72" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G72" t="s">
         <v>398</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B73">
         <v>17</v>
@@ -4112,7 +4124,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B74">
         <v>17</v>
@@ -4132,7 +4144,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B75">
         <v>17</v>
@@ -4152,7 +4164,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B76">
         <v>17</v>
@@ -4172,7 +4184,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B77">
         <v>17</v>
@@ -4192,7 +4204,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B78">
         <v>17</v>
@@ -4212,7 +4224,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B79">
         <v>17</v>
@@ -4232,7 +4244,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B80">
         <v>17</v>
@@ -4252,7 +4264,7 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B81">
         <v>17</v>
@@ -4272,10 +4284,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B82">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D82" t="s">
         <v>396</v>
@@ -4292,10 +4304,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B83">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D83" t="s">
         <v>396</v>
@@ -4308,11 +4320,14 @@
       </c>
       <c r="G83" t="s">
         <v>398</v>
+      </c>
+      <c r="H83" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B84">
         <v>15</v>
@@ -4329,16 +4344,13 @@
       <c r="G84" t="s">
         <v>398</v>
       </c>
-      <c r="H84" t="s">
-        <v>445</v>
-      </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B85">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D85" t="s">
         <v>396</v>
@@ -4355,7 +4367,7 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B86">
         <v>14</v>
@@ -4375,7 +4387,7 @@
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B87">
         <v>14</v>
@@ -4395,10 +4407,10 @@
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B88">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D88" t="s">
         <v>396</v>
@@ -4415,7 +4427,7 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B89">
         <v>13</v>
@@ -4432,10 +4444,13 @@
       <c r="G89" t="s">
         <v>398</v>
       </c>
+      <c r="H89" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B90">
         <v>13</v>
@@ -4452,13 +4467,10 @@
       <c r="G90" t="s">
         <v>398</v>
       </c>
-      <c r="H90" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B91">
         <v>13</v>
@@ -4478,10 +4490,10 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B92">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D92" t="s">
         <v>396</v>
@@ -4498,7 +4510,7 @@
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B93">
         <v>12</v>
@@ -4515,10 +4527,13 @@
       <c r="G93" t="s">
         <v>398</v>
       </c>
+      <c r="H93" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B94">
         <v>12</v>
@@ -4535,13 +4550,10 @@
       <c r="G94" t="s">
         <v>398</v>
       </c>
-      <c r="H94" t="s">
-        <v>446</v>
-      </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B95">
         <v>12</v>
@@ -4561,7 +4573,7 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B96">
         <v>12</v>
@@ -4581,10 +4593,10 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B97">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D97" t="s">
         <v>396</v>
@@ -4597,11 +4609,14 @@
       </c>
       <c r="G97" t="s">
         <v>398</v>
+      </c>
+      <c r="H97" t="s">
+        <v>441</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B98">
         <v>11</v>
@@ -4618,13 +4633,10 @@
       <c r="G98" t="s">
         <v>398</v>
       </c>
-      <c r="H98" t="s">
-        <v>441</v>
-      </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B99">
         <v>11</v>
@@ -4644,7 +4656,7 @@
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B100">
         <v>11</v>
@@ -4664,7 +4676,7 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B101">
         <v>11</v>
@@ -4684,10 +4696,10 @@
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B102">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D102" t="s">
         <v>396</v>
@@ -4700,11 +4712,14 @@
       </c>
       <c r="G102" t="s">
         <v>398</v>
+      </c>
+      <c r="H102" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B103">
         <v>10</v>
@@ -4721,13 +4736,10 @@
       <c r="G103" t="s">
         <v>398</v>
       </c>
-      <c r="H103" t="s">
-        <v>448</v>
-      </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B104">
         <v>10</v>
@@ -4747,7 +4759,7 @@
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B105">
         <v>10</v>
@@ -4767,7 +4779,7 @@
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B106">
         <v>10</v>
@@ -4787,7 +4799,7 @@
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B107">
         <v>10</v>
@@ -4804,10 +4816,13 @@
       <c r="G107" t="s">
         <v>398</v>
       </c>
+      <c r="H107" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B108">
         <v>10</v>
@@ -4824,59 +4839,59 @@
       <c r="G108" t="s">
         <v>398</v>
       </c>
-      <c r="H108" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B109">
         <v>10</v>
       </c>
       <c r="D109" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E109" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F109" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G109" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H109" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B110">
         <v>10</v>
       </c>
       <c r="D110" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E110" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F110" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G110" t="s">
-        <v>18</v>
+        <v>447</v>
       </c>
       <c r="H110" t="s">
-        <v>474</v>
+        <v>104</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B111">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D111" t="s">
         <v>396</v>
@@ -4888,15 +4903,15 @@
         <v>398</v>
       </c>
       <c r="G111" t="s">
-        <v>447</v>
+        <v>398</v>
       </c>
       <c r="H111" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B112">
         <v>9</v>
@@ -4913,13 +4928,10 @@
       <c r="G112" t="s">
         <v>398</v>
       </c>
-      <c r="H112" t="s">
-        <v>11</v>
-      </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B113">
         <v>9</v>
@@ -4938,8 +4950,8 @@
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>111</v>
+      <c r="A114">
+        <v>6320</v>
       </c>
       <c r="B114">
         <v>9</v>
@@ -4958,11 +4970,11 @@
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115">
-        <v>6320</v>
+      <c r="A115" t="s">
+        <v>112</v>
       </c>
       <c r="B115">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D115" t="s">
         <v>396</v>
@@ -4975,14 +4987,17 @@
       </c>
       <c r="G115" t="s">
         <v>398</v>
+      </c>
+      <c r="H115" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B116">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D116" t="s">
         <v>396</v>
@@ -4995,17 +5010,14 @@
       </c>
       <c r="G116" t="s">
         <v>398</v>
-      </c>
-      <c r="H116" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B117">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D117" t="s">
         <v>396</v>
@@ -5022,7 +5034,7 @@
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B118">
         <v>8</v>
@@ -5042,7 +5054,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B119">
         <v>8</v>
@@ -5062,7 +5074,7 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B120">
         <v>8</v>
@@ -5082,10 +5094,10 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>117</v>
+        <v>401</v>
       </c>
       <c r="B121">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D121" t="s">
         <v>396</v>
@@ -5102,10 +5114,10 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>401</v>
+        <v>118</v>
       </c>
       <c r="B122">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D122" t="s">
         <v>396</v>
@@ -5119,10 +5131,13 @@
       <c r="G122" t="s">
         <v>398</v>
       </c>
+      <c r="H122" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
-        <v>118</v>
+      <c r="A123">
+        <v>6218</v>
       </c>
       <c r="B123">
         <v>8</v>
@@ -5139,16 +5154,13 @@
       <c r="G123" t="s">
         <v>398</v>
       </c>
-      <c r="H123" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A124">
-        <v>6218</v>
+      <c r="A124" t="s">
+        <v>119</v>
       </c>
       <c r="B124">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D124" t="s">
         <v>396</v>
@@ -5165,10 +5177,10 @@
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B125">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D125" t="s">
         <v>396</v>
@@ -5181,14 +5193,17 @@
       </c>
       <c r="G125" t="s">
         <v>398</v>
+      </c>
+      <c r="H125" t="s">
+        <v>449</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B126">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D126" t="s">
         <v>396</v>
@@ -5201,14 +5216,11 @@
       </c>
       <c r="G126" t="s">
         <v>398</v>
-      </c>
-      <c r="H126" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B127">
         <v>7</v>
@@ -5225,10 +5237,13 @@
       <c r="G127" t="s">
         <v>398</v>
       </c>
+      <c r="H127" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B128">
         <v>7</v>
@@ -5245,13 +5260,10 @@
       <c r="G128" t="s">
         <v>398</v>
       </c>
-      <c r="H128" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B129">
         <v>7</v>
@@ -5271,7 +5283,7 @@
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B130">
         <v>7</v>
@@ -5291,7 +5303,7 @@
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B131">
         <v>7</v>
@@ -5308,10 +5320,13 @@
       <c r="G131" t="s">
         <v>398</v>
       </c>
+      <c r="H131" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B132">
         <v>7</v>
@@ -5328,13 +5343,10 @@
       <c r="G132" t="s">
         <v>398</v>
       </c>
-      <c r="H132" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B133">
         <v>7</v>
@@ -5351,10 +5363,13 @@
       <c r="G133" t="s">
         <v>398</v>
       </c>
+      <c r="H133" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B134">
         <v>7</v>
@@ -5371,16 +5386,13 @@
       <c r="G134" t="s">
         <v>398</v>
       </c>
-      <c r="H134" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B135">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D135" t="s">
         <v>396</v>
@@ -5397,7 +5409,7 @@
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B136">
         <v>6</v>
@@ -5417,10 +5429,10 @@
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B137">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D137" t="s">
         <v>396</v>
@@ -5437,10 +5449,10 @@
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B138">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D138" t="s">
         <v>396</v>
@@ -5457,7 +5469,7 @@
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B139">
         <v>6</v>
@@ -5477,7 +5489,7 @@
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B140">
         <v>6</v>
@@ -5494,10 +5506,13 @@
       <c r="G140" t="s">
         <v>398</v>
       </c>
+      <c r="H140" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B141">
         <v>6</v>
@@ -5514,13 +5529,10 @@
       <c r="G141" t="s">
         <v>398</v>
       </c>
-      <c r="H141" t="s">
-        <v>23</v>
-      </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B142">
         <v>6</v>
@@ -5540,7 +5552,7 @@
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B143">
         <v>6</v>
@@ -5560,7 +5572,7 @@
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B144">
         <v>6</v>
@@ -5580,7 +5592,7 @@
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B145">
         <v>6</v>
@@ -5600,7 +5612,7 @@
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B146">
         <v>6</v>
@@ -5620,7 +5632,7 @@
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B147">
         <v>6</v>
@@ -5640,10 +5652,10 @@
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B148">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D148" t="s">
         <v>396</v>
@@ -5656,11 +5668,14 @@
       </c>
       <c r="G148" t="s">
         <v>398</v>
+      </c>
+      <c r="H148" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B149">
         <v>5</v>
@@ -5677,13 +5692,10 @@
       <c r="G149" t="s">
         <v>398</v>
       </c>
-      <c r="H149" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B150">
         <v>5</v>
@@ -5703,7 +5715,7 @@
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B151">
         <v>5</v>
@@ -5723,7 +5735,7 @@
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B152">
         <v>5</v>
@@ -5743,7 +5755,7 @@
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B153">
         <v>5</v>
@@ -5763,7 +5775,7 @@
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B154">
         <v>5</v>
@@ -5783,7 +5795,7 @@
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B155">
         <v>5</v>
@@ -5803,7 +5815,7 @@
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B156">
         <v>5</v>
@@ -5823,7 +5835,7 @@
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B157">
         <v>5</v>
@@ -5842,8 +5854,8 @@
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
-        <v>152</v>
+      <c r="A158">
+        <v>8425</v>
       </c>
       <c r="B158">
         <v>5</v>
@@ -5862,11 +5874,11 @@
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A159">
-        <v>8425</v>
+      <c r="A159" t="s">
+        <v>153</v>
       </c>
       <c r="B159">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D159" t="s">
         <v>396</v>
@@ -5883,7 +5895,7 @@
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B160">
         <v>4</v>
@@ -5903,7 +5915,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B161">
         <v>4</v>
@@ -5923,7 +5935,7 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B162">
         <v>4</v>
@@ -5943,27 +5955,30 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B163">
         <v>4</v>
       </c>
       <c r="D163" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E163" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F163" t="s">
         <v>398</v>
       </c>
       <c r="G163" t="s">
         <v>398</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B164">
         <v>4</v>
@@ -5971,7 +5986,7 @@
       <c r="D164" t="s">
         <v>398</v>
       </c>
-      <c r="E164" t="s">
+      <c r="E164" s="1" t="s">
         <v>396</v>
       </c>
       <c r="F164" t="s">
@@ -5981,12 +5996,12 @@
         <v>398</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B165">
         <v>4</v>
@@ -6004,21 +6019,21 @@
         <v>398</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>406</v>
+        <v>450</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B166">
         <v>4</v>
       </c>
       <c r="D166" t="s">
-        <v>398</v>
-      </c>
-      <c r="E166" s="1" t="s">
-        <v>396</v>
+        <v>396</v>
+      </c>
+      <c r="E166" t="s">
+        <v>398</v>
       </c>
       <c r="F166" t="s">
         <v>398</v>
@@ -6027,21 +6042,21 @@
         <v>398</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B167">
         <v>4</v>
       </c>
       <c r="D167" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E167" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F167" t="s">
         <v>398</v>
@@ -6049,13 +6064,16 @@
       <c r="G167" t="s">
         <v>398</v>
       </c>
+      <c r="H167" t="s">
+        <v>471</v>
+      </c>
       <c r="I167" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B168">
         <v>4</v>
@@ -6063,7 +6081,7 @@
       <c r="D168" t="s">
         <v>398</v>
       </c>
-      <c r="E168" t="s">
+      <c r="E168" s="1" t="s">
         <v>396</v>
       </c>
       <c r="F168" t="s">
@@ -6072,25 +6090,22 @@
       <c r="G168" t="s">
         <v>398</v>
       </c>
-      <c r="H168" t="s">
-        <v>471</v>
-      </c>
       <c r="I168" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B169">
         <v>4</v>
       </c>
       <c r="D169" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F169" t="s">
         <v>398</v>
@@ -6098,74 +6113,74 @@
       <c r="G169" t="s">
         <v>398</v>
       </c>
+      <c r="H169" t="s">
+        <v>10</v>
+      </c>
       <c r="I169" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B170">
         <v>4</v>
       </c>
       <c r="D170" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F170" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G170" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="H170" t="s">
-        <v>10</v>
+        <v>475</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B171">
         <v>4</v>
       </c>
       <c r="D171" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F171" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G171" t="s">
-        <v>18</v>
-      </c>
-      <c r="H171" t="s">
-        <v>475</v>
+        <v>398</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B172">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F172" t="s">
         <v>398</v>
@@ -6173,22 +6188,23 @@
       <c r="G172" t="s">
         <v>398</v>
       </c>
+      <c r="H172" s="3"/>
       <c r="I172" s="3" t="s">
-        <v>456</v>
+        <v>472</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B173">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D173" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F173" t="s">
         <v>398</v>
@@ -6196,14 +6212,13 @@
       <c r="G173" t="s">
         <v>398</v>
       </c>
-      <c r="H173" s="3"/>
       <c r="I173" s="3" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B174">
         <v>4</v>
@@ -6221,18 +6236,18 @@
         <v>398</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B175">
         <v>4</v>
       </c>
       <c r="D175" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E175" s="1" t="s">
         <v>396</v>
@@ -6244,21 +6259,21 @@
         <v>398</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B176">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D176" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F176" t="s">
         <v>398</v>
@@ -6267,15 +6282,15 @@
         <v>398</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B177">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D177" t="s">
         <v>396</v>
@@ -6290,21 +6305,21 @@
         <v>398</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B178">
         <v>4</v>
       </c>
       <c r="D178" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F178" t="s">
         <v>398</v>
@@ -6313,12 +6328,12 @@
         <v>398</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B179">
         <v>4</v>
@@ -6336,20 +6351,20 @@
         <v>398</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A180" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B180">
         <v>4</v>
       </c>
       <c r="D180" t="s">
-        <v>398</v>
-      </c>
-      <c r="E180" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="E180" t="s">
         <v>396</v>
       </c>
       <c r="F180" t="s">
@@ -6359,20 +6374,20 @@
         <v>398</v>
       </c>
       <c r="I180" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A181" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B181">
         <v>4</v>
       </c>
       <c r="D181" t="s">
-        <v>400</v>
-      </c>
-      <c r="E181" t="s">
+        <v>398</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>396</v>
       </c>
       <c r="F181" t="s">
@@ -6382,61 +6397,61 @@
         <v>398</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B182">
         <v>4</v>
       </c>
       <c r="D182" t="s">
-        <v>398</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>396</v>
+        <v>18</v>
+      </c>
+      <c r="E182" t="s">
+        <v>18</v>
       </c>
       <c r="F182" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G182" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H182" t="s">
+        <v>473</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B183">
         <v>4</v>
       </c>
       <c r="D183" t="s">
-        <v>18</v>
-      </c>
-      <c r="E183" t="s">
-        <v>18</v>
+        <v>398</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="F183" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G183" t="s">
-        <v>18</v>
-      </c>
-      <c r="H183" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A184" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B184">
         <v>4</v>
@@ -6454,21 +6469,21 @@
         <v>398</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A185" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B185">
         <v>4</v>
       </c>
       <c r="D185" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F185" t="s">
         <v>398</v>
@@ -6477,21 +6492,21 @@
         <v>398</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A186" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B186">
         <v>4</v>
       </c>
       <c r="D186" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F186" t="s">
         <v>398</v>
@@ -6500,21 +6515,21 @@
         <v>398</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A187" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B187">
         <v>4</v>
       </c>
       <c r="D187" t="s">
-        <v>398</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>396</v>
+        <v>396</v>
+      </c>
+      <c r="E187" t="s">
+        <v>398</v>
       </c>
       <c r="F187" t="s">
         <v>398</v>
@@ -6522,22 +6537,23 @@
       <c r="G187" t="s">
         <v>398</v>
       </c>
+      <c r="H187" s="3"/>
       <c r="I187" s="3" t="s">
-        <v>470</v>
+        <v>408</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A188" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B188">
         <v>4</v>
       </c>
       <c r="D188" t="s">
-        <v>396</v>
-      </c>
-      <c r="E188" t="s">
-        <v>398</v>
+        <v>398</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="F188" t="s">
         <v>398</v>
@@ -6547,12 +6563,12 @@
       </c>
       <c r="H188" s="3"/>
       <c r="I188" s="3" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A189" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B189">
         <v>4</v>
@@ -6576,51 +6592,51 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A190" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B190">
         <v>4</v>
       </c>
       <c r="D190" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F190" t="s">
         <v>398</v>
       </c>
       <c r="G190" t="s">
         <v>398</v>
-      </c>
-      <c r="H190" s="3"/>
-      <c r="I190" s="3" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B191">
         <v>4</v>
       </c>
       <c r="D191" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F191" t="s">
         <v>398</v>
       </c>
       <c r="G191" t="s">
         <v>398</v>
+      </c>
+      <c r="H191" s="3"/>
+      <c r="I191" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B192">
         <v>4</v>
@@ -6628,7 +6644,7 @@
       <c r="D192" t="s">
         <v>398</v>
       </c>
-      <c r="E192" s="1" t="s">
+      <c r="E192" t="s">
         <v>396</v>
       </c>
       <c r="F192" t="s">
@@ -6644,7 +6660,7 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B193">
         <v>4</v>
@@ -6668,13 +6684,13 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B194">
         <v>4</v>
       </c>
       <c r="D194" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E194" t="s">
         <v>396</v>
@@ -6692,13 +6708,13 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B195">
         <v>4</v>
       </c>
       <c r="D195" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E195" t="s">
         <v>396</v>
@@ -6716,13 +6732,13 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B196">
         <v>4</v>
       </c>
       <c r="D196" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E196" t="s">
         <v>396</v>
@@ -6740,40 +6756,36 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B197">
         <v>4</v>
       </c>
       <c r="D197" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E197" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F197" t="s">
         <v>398</v>
       </c>
       <c r="G197" t="s">
         <v>398</v>
-      </c>
-      <c r="H197" s="3"/>
-      <c r="I197" s="3" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B198">
         <v>4</v>
       </c>
       <c r="D198" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E198" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F198" t="s">
         <v>398</v>
@@ -6781,19 +6793,23 @@
       <c r="G198" t="s">
         <v>398</v>
       </c>
+      <c r="H198" s="3"/>
+      <c r="I198" s="3" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A199" t="s">
-        <v>192</v>
+      <c r="A199" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="B199">
         <v>4</v>
       </c>
       <c r="D199" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E199" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F199" t="s">
         <v>398</v>
@@ -6801,23 +6817,23 @@
       <c r="G199" t="s">
         <v>398</v>
       </c>
-      <c r="H199" s="3"/>
-      <c r="I199" s="3" t="s">
-        <v>405</v>
-      </c>
+      <c r="H199" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I199" s="3"/>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A200" s="2" t="s">
-        <v>193</v>
+      <c r="A200" t="s">
+        <v>194</v>
       </c>
       <c r="B200">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D200" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E200" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F200" t="s">
         <v>398</v>
@@ -6825,23 +6841,23 @@
       <c r="G200" t="s">
         <v>398</v>
       </c>
-      <c r="H200" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I200" s="3"/>
+      <c r="H200" s="3"/>
+      <c r="I200" s="3" t="s">
+        <v>407</v>
+      </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B201">
         <v>3</v>
       </c>
       <c r="D201" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E201" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F201" t="s">
         <v>398</v>
@@ -6851,12 +6867,12 @@
       </c>
       <c r="H201" s="3"/>
       <c r="I201" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B202">
         <v>3</v>
@@ -6873,87 +6889,87 @@
       <c r="G202" t="s">
         <v>398</v>
       </c>
-      <c r="H202" s="3"/>
-      <c r="I202" s="3" t="s">
-        <v>409</v>
-      </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B203">
         <v>3</v>
       </c>
       <c r="D203" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E203" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F203" t="s">
         <v>398</v>
       </c>
       <c r="G203" t="s">
         <v>398</v>
+      </c>
+      <c r="H203" s="3"/>
+      <c r="I203" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B204">
         <v>3</v>
       </c>
       <c r="D204" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E204" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F204" t="s">
         <v>398</v>
       </c>
       <c r="G204" t="s">
         <v>398</v>
-      </c>
-      <c r="H204" s="3"/>
-      <c r="I204" s="3" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B205">
         <v>3</v>
       </c>
       <c r="D205" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E205" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F205" t="s">
         <v>398</v>
       </c>
       <c r="G205" t="s">
         <v>398</v>
+      </c>
+      <c r="H205" s="3"/>
+      <c r="I205" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B206">
         <v>3</v>
       </c>
       <c r="D206" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E206" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F206" t="s">
         <v>398</v>
@@ -6961,37 +6977,33 @@
       <c r="G206" t="s">
         <v>398</v>
       </c>
-      <c r="H206" s="3"/>
-      <c r="I206" s="3" t="s">
-        <v>405</v>
+      <c r="H206" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B207">
         <v>3</v>
       </c>
       <c r="D207" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E207" t="s">
         <v>398</v>
       </c>
       <c r="F207" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G207" t="s">
         <v>398</v>
-      </c>
-      <c r="H207" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B208">
         <v>3</v>
@@ -7011,19 +7023,19 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B209">
         <v>3</v>
       </c>
       <c r="D209" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E209" t="s">
         <v>398</v>
       </c>
       <c r="F209" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G209" t="s">
         <v>398</v>
@@ -7031,7 +7043,7 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B210">
         <v>3</v>
@@ -7051,7 +7063,7 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B211">
         <v>3</v>
@@ -7071,125 +7083,125 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B212">
         <v>3</v>
       </c>
       <c r="D212" t="s">
-        <v>396</v>
-      </c>
-      <c r="E212" t="s">
-        <v>398</v>
+        <v>398</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>396</v>
       </c>
       <c r="F212" t="s">
         <v>398</v>
       </c>
       <c r="G212" t="s">
         <v>398</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B213">
         <v>3</v>
       </c>
       <c r="D213" t="s">
-        <v>398</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>396</v>
+        <v>18</v>
+      </c>
+      <c r="E213" t="s">
+        <v>18</v>
       </c>
       <c r="F213" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G213" t="s">
-        <v>398</v>
-      </c>
-      <c r="I213" s="3" t="s">
-        <v>405</v>
+        <v>18</v>
+      </c>
+      <c r="H213" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B214">
         <v>3</v>
       </c>
       <c r="D214" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E214" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F214" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G214" t="s">
-        <v>18</v>
-      </c>
-      <c r="H214" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B215">
         <v>3</v>
       </c>
       <c r="D215" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E215" t="s">
         <v>398</v>
       </c>
       <c r="F215" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G215" t="s">
         <v>398</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B216">
         <v>3</v>
       </c>
       <c r="D216" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E216" t="s">
         <v>398</v>
       </c>
       <c r="F216" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G216" t="s">
         <v>398</v>
-      </c>
-      <c r="I216" s="3" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B217">
         <v>3</v>
       </c>
       <c r="D217" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E217" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F217" t="s">
         <v>398</v>
@@ -7200,7 +7212,7 @@
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B218">
         <v>3</v>
@@ -7217,33 +7229,33 @@
       <c r="G218" t="s">
         <v>398</v>
       </c>
+      <c r="I218" s="3" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>212</v>
+        <v>67</v>
       </c>
       <c r="B219">
         <v>3</v>
       </c>
       <c r="D219" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E219" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F219" t="s">
         <v>398</v>
       </c>
       <c r="G219" t="s">
         <v>398</v>
-      </c>
-      <c r="I219" s="3" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>67</v>
+        <v>213</v>
       </c>
       <c r="B220">
         <v>3</v>
@@ -7263,7 +7275,7 @@
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B221">
         <v>3</v>
@@ -7283,7 +7295,7 @@
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B222">
         <v>3</v>
@@ -7303,7 +7315,7 @@
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B223">
         <v>3</v>
@@ -7323,7 +7335,7 @@
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B224">
         <v>3</v>
@@ -7343,7 +7355,7 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B225">
         <v>3</v>
@@ -7363,7 +7375,7 @@
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B226">
         <v>3</v>
@@ -7383,7 +7395,7 @@
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B227">
         <v>3</v>
@@ -7403,73 +7415,73 @@
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B228">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D228" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E228" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F228" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G228" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H228" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A229" t="s">
-        <v>221</v>
+      <c r="A229" s="4" t="s">
+        <v>222</v>
       </c>
       <c r="B229">
         <v>2</v>
       </c>
       <c r="D229" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E229" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F229" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="G229" t="s">
-        <v>18</v>
-      </c>
-      <c r="H229" t="s">
-        <v>473</v>
+        <v>398</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A230" s="4" t="s">
-        <v>222</v>
+      <c r="A230" t="s">
+        <v>223</v>
       </c>
       <c r="B230">
         <v>2</v>
       </c>
       <c r="D230" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E230" t="s">
         <v>398</v>
       </c>
       <c r="F230" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G230" t="s">
         <v>398</v>
-      </c>
-      <c r="I230" s="3" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B231">
         <v>2</v>
@@ -7489,7 +7501,7 @@
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
-        <v>224</v>
+        <v>132</v>
       </c>
       <c r="B232">
         <v>2</v>
@@ -7509,50 +7521,50 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
-        <v>132</v>
+        <v>225</v>
       </c>
       <c r="B233">
         <v>2</v>
       </c>
       <c r="D233" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E233" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F233" t="s">
         <v>398</v>
       </c>
       <c r="G233" t="s">
         <v>398</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B234">
         <v>2</v>
       </c>
       <c r="D234" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E234" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F234" t="s">
         <v>398</v>
       </c>
       <c r="G234" t="s">
         <v>398</v>
-      </c>
-      <c r="I234" s="3" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B235">
         <v>2</v>
@@ -7572,62 +7584,62 @@
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B236">
         <v>2</v>
       </c>
       <c r="D236" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E236" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F236" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G236" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H236" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A237" t="s">
-        <v>228</v>
+      <c r="A237">
+        <v>2087</v>
       </c>
       <c r="B237">
         <v>2</v>
       </c>
       <c r="D237" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E237" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F237" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G237" t="s">
-        <v>18</v>
-      </c>
-      <c r="H237" t="s">
-        <v>474</v>
+        <v>398</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A238">
-        <v>2087</v>
+      <c r="A238" t="s">
+        <v>229</v>
       </c>
       <c r="B238">
         <v>2</v>
       </c>
       <c r="D238" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E238" t="s">
         <v>398</v>
       </c>
       <c r="F238" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G238" t="s">
         <v>398</v>
@@ -7635,7 +7647,7 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B239">
         <v>2</v>
@@ -7652,10 +7664,13 @@
       <c r="G239" t="s">
         <v>398</v>
       </c>
+      <c r="I239" s="3" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B240">
         <v>2</v>
@@ -7664,67 +7679,64 @@
         <v>398</v>
       </c>
       <c r="E240" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F240" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G240" t="s">
         <v>398</v>
-      </c>
-      <c r="I240" s="3" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B241">
         <v>2</v>
       </c>
       <c r="D241" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E241" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F241" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G241" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H241" t="s">
+        <v>473</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B242">
         <v>2</v>
       </c>
       <c r="D242" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E242" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F242" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G242" t="s">
-        <v>18</v>
-      </c>
-      <c r="H242" t="s">
-        <v>473</v>
-      </c>
-      <c r="I242" s="3" t="s">
-        <v>427</v>
+        <v>398</v>
       </c>
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B243">
         <v>2</v>
@@ -7744,7 +7756,7 @@
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B244">
         <v>2</v>
@@ -7764,7 +7776,7 @@
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B245">
         <v>2</v>
@@ -7784,7 +7796,7 @@
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
-        <v>236</v>
+        <v>37</v>
       </c>
       <c r="B246">
         <v>2</v>
@@ -7804,13 +7816,13 @@
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
-        <v>37</v>
+        <v>238</v>
       </c>
       <c r="B247">
         <v>2</v>
       </c>
       <c r="D247" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E247" t="s">
         <v>398</v>
@@ -7820,11 +7832,14 @@
       </c>
       <c r="G247" t="s">
         <v>398</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B248">
         <v>2</v>
@@ -7836,30 +7851,27 @@
         <v>398</v>
       </c>
       <c r="F248" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G248" t="s">
         <v>398</v>
-      </c>
-      <c r="I248" s="3" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B249">
         <v>2</v>
       </c>
       <c r="D249" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E249" t="s">
         <v>398</v>
       </c>
       <c r="F249" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G249" t="s">
         <v>398</v>
@@ -7867,7 +7879,7 @@
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
-        <v>240</v>
+        <v>7</v>
       </c>
       <c r="B250">
         <v>2</v>
@@ -7887,7 +7899,7 @@
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A251" t="s">
-        <v>7</v>
+        <v>241</v>
       </c>
       <c r="B251">
         <v>2</v>
@@ -7907,7 +7919,7 @@
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B252">
         <v>2</v>
@@ -7927,7 +7939,7 @@
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B253">
         <v>2</v>
@@ -7947,7 +7959,7 @@
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B254">
         <v>2</v>
@@ -7967,7 +7979,7 @@
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B255">
         <v>2</v>
@@ -7987,7 +7999,7 @@
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B256">
         <v>2</v>
@@ -8004,10 +8016,13 @@
       <c r="G256" t="s">
         <v>398</v>
       </c>
+      <c r="I256" s="3" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B257">
         <v>2</v>
@@ -8024,13 +8039,10 @@
       <c r="G257" t="s">
         <v>398</v>
       </c>
-      <c r="I257" s="3" t="s">
-        <v>412</v>
-      </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B258">
         <v>2</v>
@@ -8050,7 +8062,7 @@
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B259">
         <v>2</v>
@@ -8069,8 +8081,8 @@
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A260" t="s">
-        <v>249</v>
+      <c r="A260" s="4" t="s">
+        <v>250</v>
       </c>
       <c r="B260">
         <v>2</v>
@@ -8089,66 +8101,66 @@
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A261" s="4" t="s">
-        <v>250</v>
+      <c r="A261" t="s">
+        <v>251</v>
       </c>
       <c r="B261">
         <v>2</v>
       </c>
       <c r="D261" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E261" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F261" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G261" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H261" t="s">
+        <v>473</v>
+      </c>
+      <c r="I261" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B262">
         <v>2</v>
       </c>
       <c r="D262" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E262" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F262" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="G262" t="s">
-        <v>18</v>
-      </c>
-      <c r="H262" t="s">
-        <v>473</v>
-      </c>
-      <c r="I262" s="3" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B263">
         <v>2</v>
       </c>
       <c r="D263" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E263" t="s">
         <v>398</v>
       </c>
       <c r="F263" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G263" t="s">
         <v>398</v>
@@ -8156,7 +8168,7 @@
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
-        <v>253</v>
+        <v>111</v>
       </c>
       <c r="B264">
         <v>2</v>
@@ -8176,7 +8188,7 @@
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
-        <v>111</v>
+        <v>254</v>
       </c>
       <c r="B265">
         <v>2</v>
@@ -8196,27 +8208,30 @@
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B266">
         <v>2</v>
       </c>
       <c r="D266" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E266" t="s">
         <v>398</v>
       </c>
       <c r="F266" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G266" t="s">
         <v>398</v>
+      </c>
+      <c r="I266" s="3" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B267">
         <v>2</v>
@@ -8233,56 +8248,53 @@
       <c r="G267" t="s">
         <v>398</v>
       </c>
-      <c r="I267" s="3" t="s">
-        <v>411</v>
-      </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B268">
         <v>2</v>
       </c>
       <c r="D268" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E268" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F268" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="G268" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H268" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B269">
         <v>2</v>
       </c>
       <c r="D269" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E269" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F269" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G269" t="s">
-        <v>18</v>
-      </c>
-      <c r="H269" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B270">
         <v>2</v>
@@ -8299,10 +8311,13 @@
       <c r="G270" t="s">
         <v>398</v>
       </c>
+      <c r="H270" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B271">
         <v>2</v>
@@ -8319,56 +8334,53 @@
       <c r="G271" t="s">
         <v>398</v>
       </c>
-      <c r="H271" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B272">
         <v>2</v>
       </c>
       <c r="D272" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E272" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F272" t="s">
         <v>398</v>
       </c>
       <c r="G272" t="s">
         <v>398</v>
+      </c>
+      <c r="I272" s="3" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B273">
         <v>2</v>
       </c>
       <c r="D273" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E273" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F273" t="s">
         <v>398</v>
       </c>
       <c r="G273" t="s">
         <v>398</v>
-      </c>
-      <c r="I273" s="3" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B274">
         <v>2</v>
@@ -8388,7 +8400,7 @@
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B275">
         <v>2</v>
@@ -8408,16 +8420,16 @@
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B276">
         <v>2</v>
       </c>
       <c r="D276" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E276" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F276" t="s">
         <v>398</v>
@@ -8428,7 +8440,7 @@
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B277">
         <v>2</v>
@@ -8448,16 +8460,16 @@
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B278">
         <v>2</v>
       </c>
       <c r="D278" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E278" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F278" t="s">
         <v>398</v>
@@ -8465,10 +8477,11 @@
       <c r="G278" t="s">
         <v>398</v>
       </c>
+      <c r="J278" s="1"/>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B279">
         <v>2</v>
@@ -8485,14 +8498,13 @@
       <c r="G279" t="s">
         <v>398</v>
       </c>
-      <c r="J279" s="1"/>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B280">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D280" t="s">
         <v>396</v>
@@ -8509,10 +8521,10 @@
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D281" t="s">
         <v>396</v>
@@ -8529,7 +8541,7 @@
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B282">
         <v>2</v>
@@ -8549,82 +8561,82 @@
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B283">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E283" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F283" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G283" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H283" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E284" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F284" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G284" t="s">
-        <v>18</v>
-      </c>
-      <c r="H284" t="s">
-        <v>473</v>
+        <v>398</v>
+      </c>
+      <c r="I284" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
-        <v>273</v>
+        <v>31</v>
       </c>
       <c r="B285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E285" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F285" t="s">
         <v>398</v>
       </c>
       <c r="G285" t="s">
         <v>398</v>
-      </c>
-      <c r="I285" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
-        <v>31</v>
+        <v>274</v>
       </c>
       <c r="B286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E286" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F286" t="s">
         <v>398</v>
@@ -8635,7 +8647,7 @@
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -8651,34 +8663,34 @@
       </c>
       <c r="G287" t="s">
         <v>398</v>
+      </c>
+      <c r="I287" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B288">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E288" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F288" t="s">
         <v>398</v>
       </c>
       <c r="G288" t="s">
         <v>398</v>
-      </c>
-      <c r="I288" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="289" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A289" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B289">
         <v>1</v>
@@ -8698,7 +8710,7 @@
     </row>
     <row r="290" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -8718,16 +8730,16 @@
     </row>
     <row r="291" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E291" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F291" t="s">
         <v>398</v>
@@ -8738,7 +8750,7 @@
     </row>
     <row r="292" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -8754,11 +8766,14 @@
       </c>
       <c r="G292" t="s">
         <v>398</v>
+      </c>
+      <c r="I292" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="293" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B293">
         <v>1</v>
@@ -8781,7 +8796,7 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B294">
         <v>1</v>
@@ -8797,66 +8812,63 @@
       </c>
       <c r="G294" t="s">
         <v>398</v>
-      </c>
-      <c r="I294" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E295" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F295" t="s">
-        <v>398</v>
-      </c>
-      <c r="G295" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="G295" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H295" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E296" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F296" t="s">
-        <v>18</v>
-      </c>
-      <c r="G296" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H296" t="s">
-        <v>473</v>
+        <v>398</v>
+      </c>
+      <c r="G296" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E297" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F297" t="s">
         <v>398</v>
@@ -8867,50 +8879,50 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B298">
         <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E298" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F298" t="s">
         <v>398</v>
       </c>
       <c r="G298" t="s">
         <v>398</v>
+      </c>
+      <c r="I298" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E299" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F299" t="s">
         <v>398</v>
       </c>
       <c r="G299" t="s">
         <v>398</v>
-      </c>
-      <c r="I299" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="300" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B300">
         <v>1</v>
@@ -8926,34 +8938,40 @@
       </c>
       <c r="G300" t="s">
         <v>398</v>
+      </c>
+      <c r="I300" s="3" t="s">
+        <v>414</v>
       </c>
     </row>
     <row r="301" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B301">
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E301" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F301" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G301" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H301" t="s">
+        <v>473</v>
       </c>
       <c r="I301" s="3" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B302">
         <v>1</v>
@@ -8974,12 +8992,12 @@
         <v>473</v>
       </c>
       <c r="I302" s="3" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
     </row>
     <row r="303" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A303" t="s">
-        <v>290</v>
+      <c r="A303">
+        <v>224</v>
       </c>
       <c r="B303">
         <v>1</v>
@@ -8997,15 +9015,15 @@
         <v>18</v>
       </c>
       <c r="H303" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="I303" s="3" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="304" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A304">
-        <v>224</v>
+      <c r="A304" t="s">
+        <v>511</v>
       </c>
       <c r="B304">
         <v>1</v>
@@ -9023,15 +9041,15 @@
         <v>18</v>
       </c>
       <c r="H304" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="I304" s="3" t="s">
-        <v>405</v>
+        <v>478</v>
       </c>
     </row>
     <row r="305" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
-        <v>511</v>
+        <v>291</v>
       </c>
       <c r="B305">
         <v>1</v>
@@ -9049,15 +9067,15 @@
         <v>18</v>
       </c>
       <c r="H305" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="I305" s="3" t="s">
-        <v>478</v>
+        <v>431</v>
       </c>
     </row>
     <row r="306" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B306">
         <v>1</v>
@@ -9078,12 +9096,12 @@
         <v>473</v>
       </c>
       <c r="I306" s="3" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B307">
         <v>1</v>
@@ -9104,61 +9122,55 @@
         <v>473</v>
       </c>
       <c r="I307" s="3" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E308" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F308" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G308" t="s">
-        <v>18</v>
-      </c>
-      <c r="H308" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="I308" s="3" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>294</v>
+        <v>34</v>
       </c>
       <c r="B309">
         <v>1</v>
       </c>
       <c r="D309" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E309" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F309" t="s">
         <v>398</v>
       </c>
       <c r="G309" t="s">
         <v>398</v>
-      </c>
-      <c r="I309" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>34</v>
+        <v>295</v>
       </c>
       <c r="B310">
         <v>1</v>
@@ -9178,7 +9190,7 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B311">
         <v>1</v>
@@ -9194,20 +9206,26 @@
       </c>
       <c r="G311" t="s">
         <v>398</v>
+      </c>
+      <c r="H311" t="s">
+        <v>151</v>
+      </c>
+      <c r="I311" s="3" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B312">
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E312" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F312" t="s">
         <v>398</v>
@@ -9215,128 +9233,122 @@
       <c r="G312" t="s">
         <v>398</v>
       </c>
-      <c r="H312" t="s">
-        <v>151</v>
-      </c>
       <c r="I312" s="3" t="s">
-        <v>480</v>
+        <v>416</v>
       </c>
     </row>
     <row r="313" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B313">
         <v>1</v>
       </c>
       <c r="D313" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E313" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F313" t="s">
         <v>398</v>
       </c>
       <c r="G313" t="s">
         <v>398</v>
-      </c>
-      <c r="I313" s="3" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="314" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B314">
         <v>1</v>
       </c>
       <c r="D314" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E314" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F314" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G314" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H314" t="s">
+        <v>473</v>
+      </c>
+      <c r="I314" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="315" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B315">
         <v>1</v>
       </c>
       <c r="D315" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E315" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F315" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G315" t="s">
-        <v>18</v>
-      </c>
-      <c r="H315" t="s">
-        <v>473</v>
-      </c>
-      <c r="I315" s="3" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B316">
         <v>1</v>
       </c>
       <c r="D316" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E316" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F316" t="s">
         <v>398</v>
       </c>
       <c r="G316" t="s">
         <v>398</v>
+      </c>
+      <c r="I316" s="3" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
-        <v>301</v>
+        <v>4</v>
       </c>
       <c r="B317">
         <v>1</v>
       </c>
       <c r="D317" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E317" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F317" t="s">
         <v>398</v>
       </c>
       <c r="G317" t="s">
         <v>398</v>
-      </c>
-      <c r="I317" s="3" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B318">
         <v>1</v>
@@ -9356,124 +9368,128 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
-        <v>48</v>
+        <v>302</v>
       </c>
       <c r="B319">
         <v>1</v>
       </c>
       <c r="D319" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E319" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F319" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G319" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H319" t="s">
+        <v>473</v>
+      </c>
+      <c r="I319" s="3" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
-        <v>302</v>
+        <v>418</v>
       </c>
       <c r="B320">
         <v>1</v>
       </c>
       <c r="D320" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E320" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F320" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G320" t="s">
-        <v>18</v>
-      </c>
-      <c r="H320" t="s">
-        <v>473</v>
-      </c>
-      <c r="I320" s="3" t="s">
-        <v>410</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="I320" s="3"/>
     </row>
     <row r="321" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A321" t="s">
-        <v>418</v>
+        <v>303</v>
       </c>
       <c r="B321">
         <v>1</v>
       </c>
       <c r="D321" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E321" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F321" t="s">
-        <v>398</v>
-      </c>
-      <c r="G321" t="s">
-        <v>398</v>
-      </c>
-      <c r="I321" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="G321" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H321" t="s">
+        <v>473</v>
+      </c>
+      <c r="I321" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="J321" s="1"/>
     </row>
     <row r="322" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A322" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B322">
         <v>1</v>
       </c>
       <c r="D322" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E322" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F322" t="s">
-        <v>18</v>
-      </c>
-      <c r="G322" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H322" t="s">
-        <v>473</v>
+        <v>398</v>
+      </c>
+      <c r="G322" t="s">
+        <v>398</v>
       </c>
       <c r="I322" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="J322" s="1"/>
+        <v>413</v>
+      </c>
     </row>
     <row r="323" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A323" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B323">
         <v>1</v>
       </c>
       <c r="D323" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E323" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F323" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G323" t="s">
-        <v>398</v>
-      </c>
-      <c r="I323" s="3" t="s">
-        <v>413</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="H323" t="s">
+        <v>473</v>
+      </c>
+      <c r="J323" s="1"/>
     </row>
     <row r="324" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A324" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B324">
         <v>1</v>
@@ -9491,13 +9507,13 @@
         <v>18</v>
       </c>
       <c r="H324" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="J324" s="1"/>
     </row>
     <row r="325" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A325" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B325">
         <v>1</v>
@@ -9515,191 +9531,190 @@
         <v>18</v>
       </c>
       <c r="H325" t="s">
-        <v>482</v>
-      </c>
-      <c r="J325" s="1"/>
+        <v>473</v>
+      </c>
     </row>
     <row r="326" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A326" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B326">
         <v>1</v>
       </c>
       <c r="D326" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E326" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F326" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G326" t="s">
-        <v>18</v>
-      </c>
-      <c r="H326" t="s">
-        <v>473</v>
+        <v>398</v>
+      </c>
+      <c r="I326" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="327" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A327" t="s">
-        <v>308</v>
+        <v>120</v>
       </c>
       <c r="B327">
         <v>1</v>
       </c>
       <c r="D327" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E327" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F327" t="s">
         <v>398</v>
       </c>
       <c r="G327" t="s">
         <v>398</v>
-      </c>
-      <c r="I327" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="328" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A328" t="s">
-        <v>120</v>
+        <v>309</v>
       </c>
       <c r="B328">
         <v>1</v>
       </c>
       <c r="D328" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E328" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F328" t="s">
         <v>398</v>
       </c>
       <c r="G328" t="s">
         <v>398</v>
+      </c>
+      <c r="I328" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="329" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A329" t="s">
-        <v>309</v>
+        <v>120</v>
       </c>
       <c r="B329">
         <v>1</v>
       </c>
       <c r="D329" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E329" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F329" t="s">
         <v>398</v>
       </c>
       <c r="G329" t="s">
         <v>398</v>
-      </c>
-      <c r="I329" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="330" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A330" t="s">
-        <v>120</v>
+        <v>310</v>
       </c>
       <c r="B330">
         <v>1</v>
       </c>
       <c r="D330" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E330" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F330" t="s">
         <v>398</v>
       </c>
       <c r="G330" t="s">
         <v>398</v>
+      </c>
+      <c r="I330" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="331" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A331" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B331">
         <v>1</v>
       </c>
       <c r="D331" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E331" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F331" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G331" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H331" t="s">
+        <v>473</v>
       </c>
       <c r="I331" s="3" t="s">
-        <v>413</v>
+        <v>483</v>
       </c>
     </row>
     <row r="332" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A332" t="s">
-        <v>311</v>
+        <v>11</v>
       </c>
       <c r="B332">
         <v>1</v>
       </c>
       <c r="D332" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E332" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F332" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G332" t="s">
-        <v>18</v>
-      </c>
-      <c r="H332" t="s">
-        <v>473</v>
-      </c>
-      <c r="I332" s="3" t="s">
-        <v>483</v>
+        <v>398</v>
       </c>
     </row>
     <row r="333" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A333" t="s">
-        <v>11</v>
+        <v>312</v>
       </c>
       <c r="B333">
         <v>1</v>
       </c>
       <c r="D333" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E333" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F333" t="s">
         <v>398</v>
       </c>
       <c r="G333" t="s">
         <v>398</v>
+      </c>
+      <c r="I333" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="334" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A334" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B334">
         <v>1</v>
@@ -9722,50 +9737,53 @@
     </row>
     <row r="335" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A335" t="s">
-        <v>313</v>
+        <v>73</v>
       </c>
       <c r="B335">
         <v>1</v>
       </c>
       <c r="D335" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E335" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F335" t="s">
         <v>398</v>
       </c>
       <c r="G335" t="s">
         <v>398</v>
-      </c>
-      <c r="I335" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="336" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A336" t="s">
-        <v>73</v>
+        <v>314</v>
       </c>
       <c r="B336">
         <v>1</v>
       </c>
       <c r="D336" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E336" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F336" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G336" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H336" t="s">
+        <v>473</v>
+      </c>
+      <c r="I336" s="3" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="337" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A337" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B337">
         <v>1</v>
@@ -9791,13 +9809,13 @@
     </row>
     <row r="338" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A338" t="s">
-        <v>315</v>
+        <v>70</v>
       </c>
       <c r="B338">
         <v>1</v>
       </c>
       <c r="D338" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E338" t="s">
         <v>18</v>
@@ -9807,17 +9825,11 @@
       </c>
       <c r="G338" t="s">
         <v>18</v>
-      </c>
-      <c r="H338" t="s">
-        <v>473</v>
-      </c>
-      <c r="I338" s="3" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="339" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A339" t="s">
-        <v>70</v>
+        <v>403</v>
       </c>
       <c r="B339">
         <v>1</v>
@@ -9826,18 +9838,18 @@
         <v>396</v>
       </c>
       <c r="E339" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F339" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G339" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
     </row>
     <row r="340" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A340" t="s">
-        <v>403</v>
+        <v>316</v>
       </c>
       <c r="B340">
         <v>1</v>
@@ -9857,7 +9869,7 @@
     </row>
     <row r="341" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A341" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B341">
         <v>1</v>
@@ -9877,73 +9889,76 @@
     </row>
     <row r="342" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A342" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B342">
         <v>1</v>
       </c>
       <c r="D342" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E342" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F342" t="s">
-        <v>398</v>
-      </c>
-      <c r="G342" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="G342" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H342" t="s">
+        <v>473</v>
+      </c>
+      <c r="I342" s="3" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="343" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A343" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B343">
         <v>1</v>
       </c>
       <c r="D343" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E343" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F343" t="s">
-        <v>18</v>
-      </c>
-      <c r="G343" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="H343" t="s">
-        <v>473</v>
-      </c>
-      <c r="I343" s="3" t="s">
-        <v>405</v>
+        <v>398</v>
+      </c>
+      <c r="G343" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="344" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A344" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B344">
         <v>1</v>
       </c>
       <c r="D344" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E344" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F344" t="s">
         <v>398</v>
       </c>
       <c r="G344" t="s">
         <v>398</v>
+      </c>
+      <c r="I344" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="345" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A345" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B345">
         <v>1</v>
@@ -9966,56 +9981,56 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A346" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B346">
         <v>1</v>
       </c>
       <c r="D346" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E346" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F346" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G346" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H346" t="s">
+        <v>482</v>
       </c>
       <c r="I346" s="3" t="s">
-        <v>420</v>
+        <v>484</v>
       </c>
     </row>
     <row r="347" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A347" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B347">
         <v>1</v>
       </c>
       <c r="D347" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E347" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F347" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G347" t="s">
-        <v>18</v>
-      </c>
-      <c r="H347" t="s">
-        <v>482</v>
+        <v>398</v>
       </c>
       <c r="I347" s="3" t="s">
-        <v>484</v>
+        <v>420</v>
       </c>
     </row>
     <row r="348" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A348" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B348">
         <v>1</v>
@@ -10038,73 +10053,70 @@
     </row>
     <row r="349" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A349" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B349">
         <v>1</v>
       </c>
       <c r="D349" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E349" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F349" t="s">
         <v>398</v>
       </c>
       <c r="G349" t="s">
         <v>398</v>
-      </c>
-      <c r="I349" s="3" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="350" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A350" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B350">
         <v>1</v>
       </c>
       <c r="D350" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E350" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F350" t="s">
         <v>398</v>
       </c>
       <c r="G350" t="s">
         <v>398</v>
+      </c>
+      <c r="I350" s="3" t="s">
+        <v>421</v>
       </c>
     </row>
     <row r="351" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A351" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B351">
         <v>1</v>
       </c>
       <c r="D351" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E351" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F351" t="s">
         <v>398</v>
       </c>
       <c r="G351" t="s">
         <v>398</v>
-      </c>
-      <c r="I351" s="3" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="352" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A352" t="s">
-        <v>327</v>
+        <v>7</v>
       </c>
       <c r="B352">
         <v>1</v>
@@ -10124,7 +10136,7 @@
     </row>
     <row r="353" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A353" t="s">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="B353">
         <v>1</v>
@@ -10144,27 +10156,30 @@
     </row>
     <row r="354" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A354" t="s">
-        <v>65</v>
+        <v>328</v>
       </c>
       <c r="B354">
         <v>1</v>
       </c>
       <c r="D354" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E354" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F354" t="s">
         <v>398</v>
       </c>
       <c r="G354" t="s">
         <v>398</v>
+      </c>
+      <c r="I354" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="355" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A355" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B355">
         <v>1</v>
@@ -10187,7 +10202,7 @@
     </row>
     <row r="356" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A356" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B356">
         <v>1</v>
@@ -10205,12 +10220,12 @@
         <v>398</v>
       </c>
       <c r="I356" s="3" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="357" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A357" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B357">
         <v>1</v>
@@ -10228,21 +10243,21 @@
         <v>398</v>
       </c>
       <c r="I357" s="3" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A358" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B358">
         <v>1</v>
       </c>
       <c r="D358" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E358" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F358" t="s">
         <v>398</v>
@@ -10251,12 +10266,12 @@
         <v>398</v>
       </c>
       <c r="I358" s="3" t="s">
-        <v>422</v>
+        <v>485</v>
       </c>
     </row>
     <row r="359" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A359" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B359">
         <v>1</v>
@@ -10272,14 +10287,11 @@
       </c>
       <c r="G359" t="s">
         <v>398</v>
-      </c>
-      <c r="I359" s="3" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A360" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B360">
         <v>1</v>
@@ -10299,13 +10311,13 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A361" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B361">
         <v>1</v>
       </c>
       <c r="D361" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E361" t="s">
         <v>398</v>
@@ -10314,12 +10326,15 @@
         <v>398</v>
       </c>
       <c r="G361" t="s">
-        <v>398</v>
+        <v>396</v>
+      </c>
+      <c r="I361" s="3" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A362" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B362">
         <v>1</v>
@@ -10328,64 +10343,64 @@
         <v>398</v>
       </c>
       <c r="E362" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F362" t="s">
         <v>398</v>
       </c>
       <c r="G362" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I362" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A363" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B363">
         <v>1</v>
       </c>
       <c r="D363" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E363" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F363" t="s">
         <v>398</v>
       </c>
       <c r="G363" t="s">
         <v>398</v>
-      </c>
-      <c r="I363" s="3" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A364" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B364">
         <v>1</v>
       </c>
       <c r="D364" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E364" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F364" t="s">
         <v>398</v>
       </c>
       <c r="G364" t="s">
         <v>398</v>
+      </c>
+      <c r="I364" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A365" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B365">
         <v>1</v>
@@ -10408,7 +10423,7 @@
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A366" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B366">
         <v>1</v>
@@ -10431,30 +10446,27 @@
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A367" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B367">
         <v>1</v>
       </c>
       <c r="D367" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E367" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F367" t="s">
         <v>398</v>
       </c>
       <c r="G367" t="s">
         <v>398</v>
-      </c>
-      <c r="I367" s="3" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="368" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A368" t="s">
-        <v>341</v>
+        <v>423</v>
       </c>
       <c r="B368">
         <v>1</v>
@@ -10474,93 +10486,93 @@
     </row>
     <row r="369" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A369" t="s">
-        <v>423</v>
+        <v>342</v>
       </c>
       <c r="B369">
         <v>1</v>
       </c>
       <c r="D369" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E369" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F369" t="s">
         <v>398</v>
       </c>
       <c r="G369" t="s">
         <v>398</v>
+      </c>
+      <c r="I369" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="370" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A370" t="s">
-        <v>342</v>
+        <v>218</v>
       </c>
       <c r="B370">
         <v>1</v>
       </c>
       <c r="D370" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E370" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F370" t="s">
         <v>398</v>
       </c>
       <c r="G370" t="s">
         <v>398</v>
-      </c>
-      <c r="I370" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="371" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A371" t="s">
-        <v>218</v>
+        <v>343</v>
       </c>
       <c r="B371">
         <v>1</v>
       </c>
       <c r="D371" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E371" t="s">
         <v>398</v>
       </c>
       <c r="F371" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G371" t="s">
         <v>398</v>
+      </c>
+      <c r="I371" s="3" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="372" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A372" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B372">
         <v>1</v>
       </c>
       <c r="D372" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E372" t="s">
         <v>398</v>
       </c>
       <c r="F372" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="G372" t="s">
         <v>398</v>
-      </c>
-      <c r="I372" s="3" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="373" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A373" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B373">
         <v>1</v>
@@ -10580,70 +10592,73 @@
     </row>
     <row r="374" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B374">
         <v>1</v>
       </c>
       <c r="D374" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E374" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F374" t="s">
         <v>398</v>
       </c>
       <c r="G374" t="s">
         <v>398</v>
+      </c>
+      <c r="I374" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="375" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B375">
         <v>1</v>
       </c>
       <c r="D375" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E375" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F375" t="s">
         <v>398</v>
       </c>
       <c r="G375" t="s">
         <v>398</v>
-      </c>
-      <c r="I375" s="3" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="376" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A376" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B376">
         <v>1</v>
       </c>
       <c r="D376" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E376" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F376" t="s">
         <v>398</v>
       </c>
       <c r="G376" t="s">
         <v>398</v>
+      </c>
+      <c r="I376" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="377" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A377" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B377">
         <v>1</v>
@@ -10666,53 +10681,53 @@
     </row>
     <row r="378" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A378" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B378">
         <v>1</v>
       </c>
       <c r="D378" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E378" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F378" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G378" t="s">
-        <v>398</v>
-      </c>
-      <c r="I378" s="3" t="s">
-        <v>420</v>
+        <v>18</v>
+      </c>
+      <c r="H378" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A379" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B379">
         <v>1</v>
       </c>
       <c r="D379" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E379" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F379" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G379" t="s">
-        <v>18</v>
-      </c>
-      <c r="H379" t="s">
-        <v>474</v>
+        <v>398</v>
+      </c>
+      <c r="I379" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A380" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B380">
         <v>1</v>
@@ -10735,7 +10750,7 @@
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A381" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B381">
         <v>1</v>
@@ -10758,7 +10773,7 @@
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A382" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B382">
         <v>1</v>
@@ -10781,7 +10796,7 @@
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A383" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B383">
         <v>1</v>
@@ -10804,7 +10819,7 @@
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A384" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B384">
         <v>1</v>
@@ -10827,16 +10842,16 @@
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A385" t="s">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="B385">
         <v>1</v>
       </c>
       <c r="D385" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E385" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F385" t="s">
         <v>398</v>
@@ -10844,22 +10859,20 @@
       <c r="G385" t="s">
         <v>398</v>
       </c>
-      <c r="I385" s="3" t="s">
-        <v>420</v>
-      </c>
+      <c r="I385" s="3"/>
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
-        <v>21</v>
+        <v>382</v>
       </c>
       <c r="B386">
         <v>1</v>
       </c>
       <c r="D386" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E386" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F386" t="s">
         <v>398</v>
@@ -10867,80 +10880,79 @@
       <c r="G386" t="s">
         <v>398</v>
       </c>
-      <c r="I386" s="3"/>
+      <c r="I386" s="3" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
-        <v>382</v>
+        <v>357</v>
       </c>
       <c r="B387">
         <v>1</v>
       </c>
       <c r="D387" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E387" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F387" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G387" t="s">
-        <v>398</v>
-      </c>
-      <c r="I387" s="3" t="s">
-        <v>419</v>
+        <v>18</v>
+      </c>
+      <c r="H387" t="s">
+        <v>486</v>
       </c>
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B388">
         <v>1</v>
       </c>
       <c r="D388" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E388" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F388" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G388" t="s">
-        <v>18</v>
-      </c>
-      <c r="H388" t="s">
-        <v>486</v>
+        <v>398</v>
+      </c>
+      <c r="I388" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="389" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
-        <v>358</v>
+        <v>218</v>
       </c>
       <c r="B389">
         <v>1</v>
       </c>
       <c r="D389" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E389" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F389" t="s">
         <v>398</v>
       </c>
       <c r="G389" t="s">
         <v>398</v>
-      </c>
-      <c r="I389" s="3" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="390" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
-        <v>218</v>
+        <v>84</v>
       </c>
       <c r="B390">
         <v>1</v>
@@ -10960,27 +10972,30 @@
     </row>
     <row r="391" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
-        <v>84</v>
+        <v>359</v>
       </c>
       <c r="B391">
         <v>1</v>
       </c>
       <c r="D391" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E391" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F391" t="s">
         <v>398</v>
       </c>
       <c r="G391" t="s">
         <v>398</v>
+      </c>
+      <c r="I391" s="3" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="392" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B392">
         <v>1</v>
@@ -10989,21 +11004,21 @@
         <v>398</v>
       </c>
       <c r="E392" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F392" t="s">
         <v>398</v>
       </c>
       <c r="G392" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="I392" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="393" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B393">
         <v>1</v>
@@ -11012,21 +11027,21 @@
         <v>398</v>
       </c>
       <c r="E393" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F393" t="s">
         <v>398</v>
       </c>
       <c r="G393" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="I393" s="3" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="394" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B394">
         <v>1</v>
@@ -11049,7 +11064,7 @@
     </row>
     <row r="395" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B395">
         <v>1</v>
@@ -11072,7 +11087,7 @@
     </row>
     <row r="396" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B396">
         <v>1</v>
@@ -11095,7 +11110,7 @@
     </row>
     <row r="397" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B397">
         <v>1</v>
@@ -11118,50 +11133,50 @@
     </row>
     <row r="398" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B398">
         <v>1</v>
       </c>
       <c r="D398" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E398" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F398" t="s">
         <v>398</v>
       </c>
       <c r="G398" t="s">
         <v>398</v>
-      </c>
-      <c r="I398" s="3" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="399" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B399">
         <v>1</v>
       </c>
       <c r="D399" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E399" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F399" t="s">
         <v>398</v>
       </c>
       <c r="G399" t="s">
         <v>398</v>
+      </c>
+      <c r="I399" s="3" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="400" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B400">
         <v>1</v>
@@ -11179,81 +11194,81 @@
         <v>398</v>
       </c>
       <c r="I400" s="3" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="401" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
-        <v>368</v>
+        <v>276</v>
       </c>
       <c r="B401">
         <v>1</v>
       </c>
       <c r="D401" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E401" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F401" t="s">
         <v>398</v>
       </c>
       <c r="G401" t="s">
         <v>398</v>
-      </c>
-      <c r="I401" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="402" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
-        <v>276</v>
+        <v>369</v>
       </c>
       <c r="B402">
         <v>1</v>
       </c>
       <c r="D402" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E402" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F402" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G402" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H402" t="s">
+        <v>473</v>
+      </c>
+      <c r="I402" s="3" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="403" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B403">
         <v>1</v>
       </c>
       <c r="D403" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E403" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F403" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G403" t="s">
-        <v>18</v>
-      </c>
-      <c r="H403" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="I403" s="3" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
     </row>
     <row r="404" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B404">
         <v>1</v>
@@ -11276,16 +11291,16 @@
     </row>
     <row r="405" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B405">
         <v>1</v>
       </c>
       <c r="D405" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E405" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F405" t="s">
         <v>398</v>
@@ -11293,138 +11308,135 @@
       <c r="G405" t="s">
         <v>398</v>
       </c>
-      <c r="I405" s="3" t="s">
-        <v>413</v>
-      </c>
+      <c r="I405" s="3"/>
     </row>
     <row r="406" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B406">
         <v>1</v>
       </c>
       <c r="D406" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E406" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F406" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G406" t="s">
-        <v>398</v>
-      </c>
-      <c r="I406" s="3"/>
+        <v>396</v>
+      </c>
+      <c r="I406" s="3" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="407" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B407">
         <v>1</v>
       </c>
       <c r="D407" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E407" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F407" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="G407" t="s">
-        <v>396</v>
+        <v>18</v>
+      </c>
+      <c r="H407" t="s">
+        <v>473</v>
       </c>
       <c r="I407" s="3" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B408">
         <v>1</v>
       </c>
       <c r="D408" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E408" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F408" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G408" t="s">
-        <v>18</v>
-      </c>
-      <c r="H408" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="I408" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B409">
         <v>1</v>
       </c>
       <c r="D409" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E409" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F409" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G409" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H409" t="s">
+        <v>473</v>
       </c>
       <c r="I409" s="3" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B410">
         <v>1</v>
       </c>
       <c r="D410" t="s">
-        <v>18</v>
+        <v>400</v>
       </c>
       <c r="E410" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F410" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G410" t="s">
-        <v>18</v>
-      </c>
-      <c r="H410" t="s">
-        <v>473</v>
-      </c>
-      <c r="I410" s="3" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A411" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B411">
         <v>1</v>
       </c>
       <c r="D411" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E411" t="s">
         <v>398</v>
@@ -11438,62 +11450,62 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B412">
         <v>1</v>
       </c>
       <c r="D412" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E412" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F412" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G412" t="s">
-        <v>396</v>
+        <v>18</v>
+      </c>
+      <c r="H412" t="s">
+        <v>487</v>
+      </c>
+      <c r="I412" s="3" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B413">
         <v>1</v>
       </c>
       <c r="D413" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E413" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F413" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G413" t="s">
-        <v>18</v>
-      </c>
-      <c r="H413" t="s">
-        <v>487</v>
-      </c>
-      <c r="I413" s="3" t="s">
-        <v>483</v>
+        <v>398</v>
       </c>
     </row>
     <row r="414" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B414">
         <v>1</v>
       </c>
       <c r="D414" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E414" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F414" t="s">
         <v>398</v>
@@ -11504,76 +11516,79 @@
     </row>
     <row r="415" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B415">
         <v>1</v>
       </c>
       <c r="D415" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E415" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F415" t="s">
         <v>398</v>
       </c>
       <c r="G415" t="s">
         <v>398</v>
+      </c>
+      <c r="H415" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="416" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B416">
         <v>1</v>
       </c>
       <c r="D416" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E416" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F416" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G416" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="H416" t="s">
-        <v>36</v>
+        <v>473</v>
+      </c>
+      <c r="I416" s="3" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="417" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B417">
         <v>1</v>
       </c>
       <c r="D417" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E417" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F417" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G417" t="s">
-        <v>18</v>
-      </c>
-      <c r="H417" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
       <c r="I417" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="418" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B418">
         <v>1</v>
@@ -11589,14 +11604,11 @@
       </c>
       <c r="G418" t="s">
         <v>398</v>
-      </c>
-      <c r="I418" s="3" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="419" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
-        <v>386</v>
+        <v>34</v>
       </c>
       <c r="B419">
         <v>1</v>
@@ -11616,50 +11628,50 @@
     </row>
     <row r="420" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
-        <v>34</v>
+        <v>387</v>
       </c>
       <c r="B420">
         <v>1</v>
       </c>
       <c r="D420" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E420" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F420" t="s">
         <v>398</v>
       </c>
       <c r="G420" t="s">
         <v>398</v>
+      </c>
+      <c r="I420" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="421" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B421">
         <v>1</v>
       </c>
       <c r="D421" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E421" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F421" t="s">
         <v>398</v>
       </c>
       <c r="G421" t="s">
         <v>398</v>
-      </c>
-      <c r="I421" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="422" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B422">
         <v>1</v>
@@ -11679,99 +11691,99 @@
     </row>
     <row r="423" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B423">
         <v>1</v>
       </c>
       <c r="D423" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E423" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F423" t="s">
         <v>398</v>
       </c>
       <c r="G423" t="s">
         <v>398</v>
+      </c>
+      <c r="I423" s="3" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="424" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B424">
         <v>1</v>
       </c>
       <c r="D424" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E424" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F424" t="s">
         <v>398</v>
       </c>
       <c r="G424" t="s">
         <v>398</v>
-      </c>
-      <c r="I424" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="425" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B425">
         <v>1</v>
       </c>
       <c r="D425" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E425" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F425" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G425" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H425" t="s">
+        <v>488</v>
+      </c>
+      <c r="I425" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="O425" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="426" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B426">
         <v>1</v>
       </c>
-      <c r="D426" t="s">
-        <v>18</v>
+      <c r="D426" s="1" t="s">
+        <v>398</v>
       </c>
       <c r="E426" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F426" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G426" t="s">
-        <v>18</v>
-      </c>
-      <c r="H426" t="s">
-        <v>488</v>
-      </c>
-      <c r="I426" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="O426" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="427" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B427">
         <v>1</v>
@@ -11791,56 +11803,56 @@
     </row>
     <row r="428" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="B428">
         <v>1</v>
       </c>
-      <c r="D428" s="1" t="s">
-        <v>398</v>
+      <c r="D428" t="s">
+        <v>18</v>
       </c>
       <c r="E428" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F428" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G428" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H428" t="s">
+        <v>473</v>
+      </c>
+      <c r="I428" s="3" t="s">
+        <v>432</v>
       </c>
     </row>
     <row r="429" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="B429">
         <v>1</v>
       </c>
       <c r="D429" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="E429" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="F429" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G429" t="s">
-        <v>18</v>
-      </c>
-      <c r="H429" t="s">
-        <v>473</v>
-      </c>
-      <c r="I429" s="3" t="s">
-        <v>432</v>
+        <v>398</v>
       </c>
     </row>
     <row r="430" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="B430">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D430" t="s">
         <v>396</v>
@@ -11856,17 +11868,14 @@
       </c>
     </row>
     <row r="431" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A431" t="s">
-        <v>402</v>
-      </c>
-      <c r="B431">
-        <v>3</v>
+      <c r="A431" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="D431" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E431" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F431" t="s">
         <v>398</v>
@@ -11876,14 +11885,14 @@
       </c>
     </row>
     <row r="432" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A432" s="1" t="s">
-        <v>75</v>
+      <c r="A432" t="s">
+        <v>489</v>
       </c>
       <c r="D432" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E432" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F432" t="s">
         <v>398</v>
@@ -11894,7 +11903,7 @@
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D433" t="s">
         <v>396</v>
@@ -11907,14 +11916,17 @@
       </c>
       <c r="G433" t="s">
         <v>398</v>
+      </c>
+      <c r="H433" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D434" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E434" t="s">
         <v>398</v>
@@ -11923,18 +11935,15 @@
         <v>398</v>
       </c>
       <c r="G434" t="s">
-        <v>398</v>
-      </c>
-      <c r="H434" t="s">
-        <v>491</v>
+        <v>396</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
-        <v>492</v>
+        <v>59</v>
       </c>
       <c r="D435" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E435" t="s">
         <v>398</v>
@@ -11943,15 +11952,15 @@
         <v>398</v>
       </c>
       <c r="G435" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
-        <v>59</v>
+        <v>493</v>
       </c>
       <c r="D436" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E436" t="s">
         <v>398</v>
@@ -11960,12 +11969,12 @@
         <v>398</v>
       </c>
       <c r="G436" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D437" t="s">
         <v>398</v>
@@ -11982,44 +11991,44 @@
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="D438" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E438" t="s">
         <v>398</v>
       </c>
-      <c r="F438" t="s">
+      <c r="F438" s="3" t="s">
         <v>398</v>
       </c>
       <c r="G438" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D439" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E439" t="s">
         <v>398</v>
       </c>
-      <c r="F439" s="3" t="s">
+      <c r="F439" t="s">
         <v>398</v>
       </c>
       <c r="G439" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D440" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E440" t="s">
         <v>398</v>
@@ -12028,55 +12037,55 @@
         <v>398</v>
       </c>
       <c r="G440" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
-        <v>497</v>
+        <v>166</v>
       </c>
       <c r="D441" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="E441" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="F441" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G441" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H441" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
-        <v>166</v>
+        <v>499</v>
       </c>
       <c r="D442" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E442" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F442" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G442" t="s">
-        <v>18</v>
-      </c>
-      <c r="H442" t="s">
-        <v>498</v>
+        <v>398</v>
       </c>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D443" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E443" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F443" t="s">
         <v>398</v>
@@ -12087,13 +12096,13 @@
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D444" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E444" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F444" t="s">
         <v>398</v>
@@ -12104,7 +12113,7 @@
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D445" t="s">
         <v>398</v>
@@ -12121,13 +12130,13 @@
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D446" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E446" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F446" t="s">
         <v>398</v>
@@ -12138,13 +12147,13 @@
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D447" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E447" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F447" t="s">
         <v>398</v>
@@ -12155,7 +12164,7 @@
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D448" t="s">
         <v>398</v>
@@ -12172,7 +12181,7 @@
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D449" t="s">
         <v>398</v>
@@ -12189,13 +12198,13 @@
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D450" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E450" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F450" t="s">
         <v>398</v>
@@ -12205,14 +12214,14 @@
       </c>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A451" t="s">
-        <v>507</v>
+      <c r="A451">
+        <v>208432</v>
       </c>
       <c r="D451" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E451" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F451" t="s">
         <v>398</v>
@@ -12222,14 +12231,14 @@
       </c>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A452">
-        <v>208432</v>
+      <c r="A452" t="s">
+        <v>508</v>
       </c>
       <c r="D452" t="s">
         <v>398</v>
       </c>
       <c r="E452" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F452" t="s">
         <v>398</v>
@@ -12240,13 +12249,13 @@
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D453" t="s">
         <v>398</v>
       </c>
       <c r="E453" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F453" t="s">
         <v>398</v>
@@ -12257,7 +12266,7 @@
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D454" t="s">
         <v>398</v>
@@ -12274,47 +12283,47 @@
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" t="s">
-        <v>510</v>
+        <v>511</v>
+      </c>
+      <c r="B455" t="s">
+        <v>18</v>
       </c>
       <c r="D455" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E455" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F455" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G455" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H455" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A456" t="s">
-        <v>511</v>
-      </c>
-      <c r="B456" t="s">
-        <v>18</v>
+      <c r="A456">
+        <v>8885</v>
       </c>
       <c r="D456" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E456" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F456" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G456" t="s">
-        <v>18</v>
-      </c>
-      <c r="H456" t="s">
-        <v>512</v>
+        <v>398</v>
       </c>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457">
-        <v>8885</v>
+        <v>9067</v>
       </c>
       <c r="D457" t="s">
         <v>398</v>
@@ -12330,8 +12339,8 @@
       </c>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A458">
-        <v>9067</v>
+      <c r="A458" t="s">
+        <v>513</v>
       </c>
       <c r="D458" t="s">
         <v>398</v>
@@ -12348,7 +12357,7 @@
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D459" t="s">
         <v>398</v>
@@ -12365,7 +12374,7 @@
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D460" t="s">
         <v>398</v>
@@ -12382,7 +12391,7 @@
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D461" t="s">
         <v>398</v>
@@ -12398,8 +12407,8 @@
       </c>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A462" t="s">
-        <v>516</v>
+      <c r="A462">
+        <v>9070</v>
       </c>
       <c r="D462" t="s">
         <v>398</v>
@@ -12416,7 +12425,7 @@
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463">
-        <v>9070</v>
+        <v>8977</v>
       </c>
       <c r="D463" t="s">
         <v>398</v>
@@ -12432,8 +12441,8 @@
       </c>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A464">
-        <v>8977</v>
+      <c r="A464" t="s">
+        <v>517</v>
       </c>
       <c r="D464" t="s">
         <v>398</v>
@@ -12450,44 +12459,44 @@
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" t="s">
-        <v>517</v>
+        <v>176</v>
       </c>
       <c r="D465" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E465" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F465" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G465" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H465" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A466" t="s">
-        <v>176</v>
+      <c r="A466">
+        <v>8948</v>
       </c>
       <c r="D466" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E466" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F466" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G466" t="s">
-        <v>18</v>
-      </c>
-      <c r="H466" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A467">
-        <v>8948</v>
+      <c r="A467" t="s">
+        <v>518</v>
       </c>
       <c r="D467" t="s">
         <v>398</v>
@@ -12504,75 +12513,75 @@
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D468" t="s">
         <v>398</v>
       </c>
       <c r="E468" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F468" t="s">
         <v>398</v>
       </c>
       <c r="G468" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D469" t="s">
         <v>398</v>
       </c>
       <c r="E469" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F469" t="s">
         <v>398</v>
       </c>
       <c r="G469" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D470" t="s">
         <v>398</v>
       </c>
       <c r="E470" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F470" t="s">
         <v>398</v>
       </c>
       <c r="G470" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A471" t="s">
-        <v>521</v>
+      <c r="A471" s="5" t="s">
+        <v>522</v>
       </c>
       <c r="D471" t="s">
         <v>398</v>
       </c>
       <c r="E471" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F471" t="s">
         <v>398</v>
       </c>
       <c r="G471" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" s="5" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D472" t="s">
         <v>398</v>
@@ -12589,7 +12598,7 @@
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" s="5" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D473" t="s">
         <v>398</v>
@@ -12606,7 +12615,7 @@
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" s="5" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="D474" t="s">
         <v>398</v>
@@ -12623,7 +12632,7 @@
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" s="5" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D475" t="s">
         <v>398</v>
@@ -12640,7 +12649,7 @@
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" s="5" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="D476" t="s">
         <v>398</v>
@@ -12657,7 +12666,7 @@
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" s="5" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D477" t="s">
         <v>398</v>
@@ -12673,8 +12682,8 @@
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A478" s="5" t="s">
-        <v>528</v>
+      <c r="A478" t="s">
+        <v>529</v>
       </c>
       <c r="D478" t="s">
         <v>398</v>
@@ -12690,8 +12699,8 @@
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A479" t="s">
-        <v>529</v>
+      <c r="A479" s="5" t="s">
+        <v>531</v>
       </c>
       <c r="D479" t="s">
         <v>398</v>
@@ -12707,8 +12716,8 @@
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A480" s="5" t="s">
-        <v>531</v>
+      <c r="A480" t="s">
+        <v>530</v>
       </c>
       <c r="D480" t="s">
         <v>398</v>
@@ -12724,8 +12733,8 @@
       </c>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A481" t="s">
-        <v>530</v>
+      <c r="A481" s="5" t="s">
+        <v>532</v>
       </c>
       <c r="D481" t="s">
         <v>398</v>
@@ -12742,7 +12751,7 @@
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A482" s="5" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D482" t="s">
         <v>398</v>
@@ -12759,7 +12768,7 @@
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A483" s="5" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D483" t="s">
         <v>398</v>
@@ -12775,8 +12784,8 @@
       </c>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A484" s="5" t="s">
-        <v>534</v>
+      <c r="A484" s="5">
+        <v>8966</v>
       </c>
       <c r="D484" t="s">
         <v>398</v>
@@ -12792,85 +12801,85 @@
       </c>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A485" s="5">
-        <v>8966</v>
+      <c r="A485" t="s">
+        <v>535</v>
       </c>
       <c r="D485" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E485" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F485" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G485" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H485" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D486" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E486" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F486" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G486" t="s">
-        <v>18</v>
-      </c>
-      <c r="H486" t="s">
-        <v>473</v>
+        <v>398</v>
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D487" t="s">
         <v>398</v>
       </c>
       <c r="E487" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F487" t="s">
         <v>398</v>
       </c>
       <c r="G487" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="D488" t="s">
         <v>398</v>
       </c>
       <c r="E488" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F488" t="s">
         <v>398</v>
       </c>
       <c r="G488" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A489" t="s">
-        <v>538</v>
+      <c r="A489" s="5" t="s">
+        <v>539</v>
       </c>
       <c r="D489" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E489" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F489" t="s">
         <v>398</v>
@@ -12880,14 +12889,14 @@
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A490" s="5" t="s">
-        <v>539</v>
+      <c r="A490" t="s">
+        <v>540</v>
       </c>
       <c r="D490" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E490" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F490" t="s">
         <v>398</v>
@@ -12898,13 +12907,13 @@
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D491" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E491" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F491" t="s">
         <v>398</v>
@@ -12915,18 +12924,30 @@
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
-        <v>541</v>
+        <v>384</v>
+      </c>
+      <c r="D492" t="s">
+        <v>396</v>
+      </c>
+      <c r="E492" t="s">
+        <v>398</v>
+      </c>
+      <c r="F492" t="s">
+        <v>398</v>
+      </c>
+      <c r="G492" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
-        <v>384</v>
+        <v>542</v>
       </c>
       <c r="D493" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E493" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F493" t="s">
         <v>398</v>
@@ -12937,207 +12958,230 @@
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="D494" t="s">
         <v>398</v>
       </c>
       <c r="E494" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F494" t="s">
         <v>398</v>
       </c>
       <c r="G494" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D495" t="s">
         <v>398</v>
       </c>
       <c r="E495" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F495" t="s">
         <v>398</v>
       </c>
       <c r="G495" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="D496" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E496" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F496" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G496" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H496" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D497" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="E497" t="s">
-        <v>18</v>
+        <v>396</v>
       </c>
       <c r="F497" t="s">
-        <v>18</v>
+        <v>398</v>
       </c>
       <c r="G497" t="s">
-        <v>18</v>
-      </c>
-      <c r="H497" t="s">
-        <v>498</v>
+        <v>398</v>
       </c>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D498" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="E498" t="s">
-        <v>396</v>
+        <v>18</v>
       </c>
       <c r="F498" t="s">
-        <v>398</v>
+        <v>18</v>
       </c>
       <c r="G498" t="s">
-        <v>398</v>
+        <v>18</v>
+      </c>
+      <c r="H498" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A499" t="s">
+        <v>549</v>
+      </c>
+      <c r="D499" t="s">
+        <v>396</v>
+      </c>
+      <c r="E499" t="s">
+        <v>398</v>
+      </c>
+      <c r="F499" t="s">
+        <v>398</v>
+      </c>
+      <c r="G499" t="s">
+        <v>398</v>
+      </c>
+      <c r="H499" t="s">
+        <v>550</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="20" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="I408" r:id="rId1" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{2280DFAF-F5F9-B44D-BB76-39B1AF7D8DC6}"/>
-    <hyperlink ref="I410" r:id="rId2" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{81CE5181-3849-844A-B6F1-E4FB7F4E32DA}"/>
-    <hyperlink ref="I164" r:id="rId3" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{314C68DA-6C76-4348-826E-107EE477A7B5}"/>
-    <hyperlink ref="I213" r:id="rId4" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{B06FD081-7C7F-EA42-B5B3-FDD74ADF9D96}"/>
-    <hyperlink ref="I216" r:id="rId5" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1629673" xr:uid="{C56212C6-9C9D-A249-BBF1-6AAAC3A04140}"/>
-    <hyperlink ref="I219" r:id="rId6" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{8AFD8791-4359-3742-92AB-5EE004B9BAEC}"/>
-    <hyperlink ref="I230" r:id="rId7" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1138538" xr:uid="{36F95E06-C721-E844-8664-43BFC48F9685}"/>
-    <hyperlink ref="I234" r:id="rId8" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{3AAE315F-F869-7D4C-A023-3354D53C1D40}"/>
-    <hyperlink ref="I248" r:id="rId9" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1138538" xr:uid="{28E00F68-E1C6-724F-B5BB-C34377A81C37}"/>
-    <hyperlink ref="I257" r:id="rId10" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL3286184" xr:uid="{499EBD83-8549-0649-9D10-42D7713400C2}"/>
-    <hyperlink ref="I267" r:id="rId11" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1138538" xr:uid="{19539332-173C-F84D-BF87-6A5178195608}"/>
-    <hyperlink ref="I240" r:id="rId12" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1138538" xr:uid="{3F3A8E46-B39C-BA41-A7FF-20FD82DB2235}"/>
-    <hyperlink ref="I273" r:id="rId13" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1138538" xr:uid="{878DF795-3DF3-D14A-AA03-DAAEE9B715B2}"/>
-    <hyperlink ref="I288" r:id="rId14" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{09A72648-C2EE-474B-8B4D-077D1B61B2A6}"/>
-    <hyperlink ref="I293" r:id="rId15" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{3EA44F54-41B4-1B41-8C0F-3A0A1DF46BCB}"/>
-    <hyperlink ref="I294" r:id="rId16" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{CAC48125-0A53-B447-8B6E-ACBD90F424F5}"/>
-    <hyperlink ref="I299" r:id="rId17" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{C6EB1FCC-739E-0446-A50A-011F5DA325D7}"/>
-    <hyperlink ref="I301" r:id="rId18" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1156420" xr:uid="{A59C96EB-32AF-3646-8682-8671D36B15E4}"/>
-    <hyperlink ref="I304" r:id="rId19" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{EED766A7-914A-C24D-961B-B2D5A6F4461B}"/>
-    <hyperlink ref="I308" r:id="rId20" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{EC605B37-CEE7-F14D-B278-1BCEF3E56AEB}"/>
-    <hyperlink ref="I309" r:id="rId21" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{076C04BC-8C5A-0445-A950-D947A3F8CA6B}"/>
-    <hyperlink ref="I313" r:id="rId22" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL2331468" xr:uid="{05495463-901D-2B41-9978-85EDA395D374}"/>
-    <hyperlink ref="I317" r:id="rId23" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL5108065" xr:uid="{575F5992-E846-D74D-B1A3-9B03098DB010}"/>
-    <hyperlink ref="I323" r:id="rId24" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{B6D88CE6-C394-844A-B937-94674F733966}"/>
-    <hyperlink ref="I327" r:id="rId25" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{49DFAFB6-2E1C-CB4C-A38E-AD69AB0D279B}"/>
-    <hyperlink ref="I329" r:id="rId26" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{0C154066-4CD7-B446-AA17-9C60B2C797C7}"/>
-    <hyperlink ref="I331" r:id="rId27" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{672F514F-B0FE-304F-A1B2-39B786514AE6}"/>
-    <hyperlink ref="I334" r:id="rId28" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{F4E6877C-D9F8-D84E-9897-205CAE430E9B}"/>
-    <hyperlink ref="I335" r:id="rId29" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{281B61D9-07D0-5D45-9A45-DDB4F0159A67}"/>
-    <hyperlink ref="I303" r:id="rId30" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{DFDBA5F5-17F9-5C41-87D1-39C389CAEA38}"/>
-    <hyperlink ref="I345" r:id="rId31" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{F663D9F1-08CC-5749-968A-7851DC6B334D}"/>
-    <hyperlink ref="I346" r:id="rId32" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{1DCCE41D-0A60-C547-AA00-799ECBCD2FA4}"/>
-    <hyperlink ref="I348" r:id="rId33" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{9EEB1B59-B5E1-5246-933C-27320078AEE1}"/>
-    <hyperlink ref="I349" r:id="rId34" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{F8763799-23B5-4146-A448-D1506A560F5B}"/>
-    <hyperlink ref="I351" r:id="rId35" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1142189" xr:uid="{0DA7D564-E6F8-BB42-96D7-1DDEC26EB7F8}"/>
-    <hyperlink ref="I355" r:id="rId36" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{FFBAA85D-5927-0644-95D8-4459806D9811}"/>
-    <hyperlink ref="I356" r:id="rId37" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{5708C9BA-98D6-0047-829A-6D81B7B4D9B0}"/>
-    <hyperlink ref="I357" r:id="rId38" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL2331468" xr:uid="{38212C86-332B-2D4F-914D-2D204BB598E0}"/>
-    <hyperlink ref="I358" r:id="rId39" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL2331468" xr:uid="{0D91B6EC-A02F-0D48-99E5-DAC51582DCA2}"/>
-    <hyperlink ref="I363" r:id="rId40" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{AA6B9E29-4208-4840-8A59-AF21218EABFD}"/>
-    <hyperlink ref="I365" r:id="rId41" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{CFAEEB80-7E3A-2F4D-B27F-0838846DB996}"/>
-    <hyperlink ref="I366" r:id="rId42" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{A2D4C8CA-E6F2-4B4F-A4F3-DB53EF714FE2}"/>
-    <hyperlink ref="I367" r:id="rId43" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{2FCC28DE-A74F-0642-ADCB-C44761CD046E}"/>
-    <hyperlink ref="I370" r:id="rId44" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{9C3B970D-D0FA-DE48-9CAC-494AE9565A2E}"/>
-    <hyperlink ref="I372" r:id="rId45" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL5126639" xr:uid="{5E1DCD8D-C70F-8D4C-AAD5-25ACF595052B}"/>
-    <hyperlink ref="I375" r:id="rId46" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{B1965716-BD98-364E-BD65-487D07D77973}"/>
-    <hyperlink ref="I377" r:id="rId47" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{F456591E-A05E-6646-9273-49AFC3D2A419}"/>
-    <hyperlink ref="I378" r:id="rId48" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{E55CB5BE-AD00-4A46-8A3F-DE98471A2BF6}"/>
-    <hyperlink ref="I380" r:id="rId49" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{A035627D-CE04-D94F-8E2C-5F00834EBFFE}"/>
-    <hyperlink ref="I381" r:id="rId50" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{D98FD7FA-4ADD-4448-931A-A13F9782A51A}"/>
-    <hyperlink ref="I383" r:id="rId51" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{4A37A8F9-88A8-BC44-9BCD-897B30A22E52}"/>
-    <hyperlink ref="I382" r:id="rId52" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{14283AA2-5FCF-4448-A1D6-5A19ADBD5F47}"/>
-    <hyperlink ref="I384" r:id="rId53" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{295E167C-BF95-1148-AB1E-DAAFBD3C5920}"/>
-    <hyperlink ref="I385" r:id="rId54" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{E7794773-D825-F049-86B7-CE1FC790B841}"/>
-    <hyperlink ref="I387" r:id="rId55" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1150789" xr:uid="{EAF6F8F3-BF61-F74E-B506-139FB7E6F864}"/>
-    <hyperlink ref="I389" r:id="rId56" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{3FE09900-81D1-6C40-A6C3-E8BEE166F4D9}"/>
-    <hyperlink ref="I394" r:id="rId57" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{B72801D8-F53E-4945-9D9C-D94552C78434}"/>
-    <hyperlink ref="I395" r:id="rId58" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{5A9F5449-1A48-E642-8944-A38E6BED13AF}"/>
-    <hyperlink ref="I396" r:id="rId59" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{EEA87C64-29CF-1C41-95D9-B0B60A1D6E44}"/>
-    <hyperlink ref="I397" r:id="rId60" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{7004252B-B169-CC4C-9976-D94705C3DC78}"/>
-    <hyperlink ref="I398" r:id="rId61" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{61E5BB24-3CC7-4C42-9CCA-C88BDCD36EA9}"/>
-    <hyperlink ref="I392" r:id="rId62" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4837227" xr:uid="{D4ED6F84-C6B6-CB4C-85E6-3D8A0053FA58}"/>
-    <hyperlink ref="I393" r:id="rId63" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671696" xr:uid="{0EBEEC98-F8D2-1541-9BF0-2E11E79074A8}"/>
-    <hyperlink ref="I400" r:id="rId64" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{AE92238E-D6C5-D540-B5EA-B653D643D0D9}"/>
-    <hyperlink ref="I401" r:id="rId65" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{9100A303-88F9-524E-99F9-B6B33AE3434B}"/>
-    <hyperlink ref="I403" r:id="rId66" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL3396969" xr:uid="{3637B675-39B4-A74F-97EA-F1124E43F56B}"/>
-    <hyperlink ref="I405" r:id="rId67" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{C5EB2FBC-F677-4048-A743-D907D7ED4DE8}"/>
-    <hyperlink ref="I404" r:id="rId68" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{A67E6A2C-B0D6-3F4D-A569-A2A59157377D}"/>
-    <hyperlink ref="I407" r:id="rId69" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL2331468" xr:uid="{78A9C280-A1C4-9A42-BE04-80AE94F5BFFE}"/>
-    <hyperlink ref="I409" r:id="rId70" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255275" xr:uid="{3997E592-AF8D-014F-B011-94477175E03B}"/>
-    <hyperlink ref="I417" r:id="rId71" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4257512" xr:uid="{6B6C4203-241E-BB4D-B0EA-BE4433D22B68}"/>
-    <hyperlink ref="I418" r:id="rId72" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL5126551" xr:uid="{E205C66B-FE91-744C-8B71-3A1698213773}"/>
-    <hyperlink ref="I421" r:id="rId73" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{3F361A3B-2DDB-D449-BB31-EA3F389FD422}"/>
-    <hyperlink ref="I424" r:id="rId74" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{0D9E7465-905E-974F-A77D-1919885ABE92}"/>
-    <hyperlink ref="I426" r:id="rId75" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL3351618" xr:uid="{22F1D2A8-3695-A047-8C92-985F272B47BD}"/>
-    <hyperlink ref="I429" r:id="rId76" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4190314" xr:uid="{EA21D424-813F-824B-8E9E-2DCD65C3DB2C}"/>
-    <hyperlink ref="I72" r:id="rId77" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1156683" xr:uid="{098C26B3-3BB2-D14F-A8B7-227BEA93B37A}"/>
-    <hyperlink ref="I31" r:id="rId78" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1156420" xr:uid="{7B186905-CF63-4D49-87D5-30F63528F7A6}"/>
-    <hyperlink ref="I173" r:id="rId79" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4706622" xr:uid="{1972A8CA-AB28-F541-AF4F-FF1D103563E9}"/>
-    <hyperlink ref="I190" r:id="rId80" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{67DD7D8E-29BB-6B41-B708-1578EF373020}"/>
-    <hyperlink ref="I189" r:id="rId81" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{0540BA7F-6858-0B4C-BAB0-9DD9E3853739}"/>
-    <hyperlink ref="I188" r:id="rId82" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671704" xr:uid="{A8E92FAF-6EFB-2A40-AA93-01AF3C1990FF}"/>
-    <hyperlink ref="I192" r:id="rId83" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{D67CB0AA-25E5-514F-B644-21EDD821BBD1}"/>
-    <hyperlink ref="I193" r:id="rId84" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{2F7688D5-D86C-704E-9FD6-017DC9C9D5F2}"/>
-    <hyperlink ref="I197" r:id="rId85" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{B37BB24E-B70F-5848-B861-A818F930BB02}"/>
-    <hyperlink ref="I196" r:id="rId86" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{6208CB76-A2D8-AF42-B6F5-DDBD26DCF5E8}"/>
-    <hyperlink ref="I195" r:id="rId87" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{AB987528-68B6-A14E-839C-40D4AD542C9A}"/>
-    <hyperlink ref="I194" r:id="rId88" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{181F1D5D-3B5F-6148-8415-4E2919C46A4C}"/>
-    <hyperlink ref="I199" r:id="rId89" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{91BF5D36-EA34-2A4C-89BA-CF4981324D64}"/>
-    <hyperlink ref="I201" r:id="rId90" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255275" xr:uid="{36E2A91C-B6EB-9047-968D-E7C175E128F4}"/>
-    <hyperlink ref="I202" r:id="rId91" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1142312" xr:uid="{39C8D12B-5BFA-1A47-8AF3-24B594666D96}"/>
-    <hyperlink ref="I204" r:id="rId92" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{55F6C0F4-59FD-194A-8F45-AB3D55B68AE7}"/>
-    <hyperlink ref="I206" r:id="rId93" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{31741F6A-BA32-314E-957E-107111237DAA}"/>
-    <hyperlink ref="I242" r:id="rId94" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL3396969" xr:uid="{1A51222E-0F97-0343-9CBE-4B6CEAC13D13}"/>
-    <hyperlink ref="I262" r:id="rId95" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{990CAD29-CB68-5C42-BB57-C47D96094A5E}"/>
-    <hyperlink ref="I285" r:id="rId96" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{4E45E8E2-0DB8-5F45-9AA2-A2886A2E4D59}"/>
-    <hyperlink ref="I302" r:id="rId97" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4190314" xr:uid="{F46F4FED-60F1-1242-B4A2-088C905DF41E}"/>
-    <hyperlink ref="I305" r:id="rId98" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL5321250" xr:uid="{865140C8-07DC-6541-A046-3320A671020C}"/>
-    <hyperlink ref="I306" r:id="rId99" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4673175" xr:uid="{BD1EBED1-5502-9348-B71E-EC8CDD06DD10}"/>
-    <hyperlink ref="I307" r:id="rId100" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{D0669686-04C4-BF47-AB56-86996728C601}"/>
-    <hyperlink ref="I312" r:id="rId101" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL5352391" xr:uid="{60810FCA-1AC8-7840-BE74-67F985EBC44D}"/>
-    <hyperlink ref="I315" r:id="rId102" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{7BD95745-F163-6545-BE5A-2C6E9EFB68BE}"/>
-    <hyperlink ref="I320" r:id="rId103" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1629673" xr:uid="{366A2F8D-F6AF-0F4A-B371-6D71464906FB}"/>
-    <hyperlink ref="I322" r:id="rId104" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4007417" xr:uid="{8848E855-7F8A-AB48-8F56-DBFB7E91472B}"/>
-    <hyperlink ref="I332" r:id="rId105" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1649199" xr:uid="{24BCBE57-8D35-1C43-ACC2-78B0FA80427A}"/>
-    <hyperlink ref="I337" r:id="rId106" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4190314" xr:uid="{2A20B166-F4A3-1B46-89F7-0D5875B6AF8E}"/>
-    <hyperlink ref="I338" r:id="rId107" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4190314" xr:uid="{11A043A8-CC67-FA4F-8F13-72CD4F8FCDFD}"/>
-    <hyperlink ref="I343" r:id="rId108" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{7C4EBA1F-194C-034F-8830-12194A50F1F5}"/>
-    <hyperlink ref="I347" r:id="rId109" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1649192" xr:uid="{23575900-4592-B047-A7D3-39DB7BAC461E}"/>
-    <hyperlink ref="I359" r:id="rId110" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1142472" xr:uid="{6C2D815C-2AD3-7843-B5E8-90561193FCE6}"/>
-    <hyperlink ref="I362" r:id="rId111" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671696" xr:uid="{005F6736-204D-EF47-8E43-4ED1288E1268}"/>
-    <hyperlink ref="I413" r:id="rId112" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1649199" xr:uid="{B4AD8135-5F1E-BB49-A85B-CFA28FDE3098}"/>
+    <hyperlink ref="I407" r:id="rId1" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{2280DFAF-F5F9-B44D-BB76-39B1AF7D8DC6}"/>
+    <hyperlink ref="I409" r:id="rId2" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{81CE5181-3849-844A-B6F1-E4FB7F4E32DA}"/>
+    <hyperlink ref="I163" r:id="rId3" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{314C68DA-6C76-4348-826E-107EE477A7B5}"/>
+    <hyperlink ref="I212" r:id="rId4" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{B06FD081-7C7F-EA42-B5B3-FDD74ADF9D96}"/>
+    <hyperlink ref="I215" r:id="rId5" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1629673" xr:uid="{C56212C6-9C9D-A249-BBF1-6AAAC3A04140}"/>
+    <hyperlink ref="I218" r:id="rId6" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{8AFD8791-4359-3742-92AB-5EE004B9BAEC}"/>
+    <hyperlink ref="I229" r:id="rId7" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1138538" xr:uid="{36F95E06-C721-E844-8664-43BFC48F9685}"/>
+    <hyperlink ref="I233" r:id="rId8" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{3AAE315F-F869-7D4C-A023-3354D53C1D40}"/>
+    <hyperlink ref="I247" r:id="rId9" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1138538" xr:uid="{28E00F68-E1C6-724F-B5BB-C34377A81C37}"/>
+    <hyperlink ref="I256" r:id="rId10" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL3286184" xr:uid="{499EBD83-8549-0649-9D10-42D7713400C2}"/>
+    <hyperlink ref="I266" r:id="rId11" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1138538" xr:uid="{19539332-173C-F84D-BF87-6A5178195608}"/>
+    <hyperlink ref="I239" r:id="rId12" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1138538" xr:uid="{3F3A8E46-B39C-BA41-A7FF-20FD82DB2235}"/>
+    <hyperlink ref="I272" r:id="rId13" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1138538" xr:uid="{878DF795-3DF3-D14A-AA03-DAAEE9B715B2}"/>
+    <hyperlink ref="I287" r:id="rId14" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{09A72648-C2EE-474B-8B4D-077D1B61B2A6}"/>
+    <hyperlink ref="I292" r:id="rId15" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{3EA44F54-41B4-1B41-8C0F-3A0A1DF46BCB}"/>
+    <hyperlink ref="I293" r:id="rId16" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{CAC48125-0A53-B447-8B6E-ACBD90F424F5}"/>
+    <hyperlink ref="I298" r:id="rId17" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{C6EB1FCC-739E-0446-A50A-011F5DA325D7}"/>
+    <hyperlink ref="I300" r:id="rId18" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1156420" xr:uid="{A59C96EB-32AF-3646-8682-8671D36B15E4}"/>
+    <hyperlink ref="I303" r:id="rId19" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{EED766A7-914A-C24D-961B-B2D5A6F4461B}"/>
+    <hyperlink ref="I307" r:id="rId20" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{EC605B37-CEE7-F14D-B278-1BCEF3E56AEB}"/>
+    <hyperlink ref="I308" r:id="rId21" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{076C04BC-8C5A-0445-A950-D947A3F8CA6B}"/>
+    <hyperlink ref="I312" r:id="rId22" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL2331468" xr:uid="{05495463-901D-2B41-9978-85EDA395D374}"/>
+    <hyperlink ref="I316" r:id="rId23" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL5108065" xr:uid="{575F5992-E846-D74D-B1A3-9B03098DB010}"/>
+    <hyperlink ref="I322" r:id="rId24" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{B6D88CE6-C394-844A-B937-94674F733966}"/>
+    <hyperlink ref="I326" r:id="rId25" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{49DFAFB6-2E1C-CB4C-A38E-AD69AB0D279B}"/>
+    <hyperlink ref="I328" r:id="rId26" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{0C154066-4CD7-B446-AA17-9C60B2C797C7}"/>
+    <hyperlink ref="I330" r:id="rId27" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{672F514F-B0FE-304F-A1B2-39B786514AE6}"/>
+    <hyperlink ref="I333" r:id="rId28" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{F4E6877C-D9F8-D84E-9897-205CAE430E9B}"/>
+    <hyperlink ref="I334" r:id="rId29" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{281B61D9-07D0-5D45-9A45-DDB4F0159A67}"/>
+    <hyperlink ref="I302" r:id="rId30" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{DFDBA5F5-17F9-5C41-87D1-39C389CAEA38}"/>
+    <hyperlink ref="I344" r:id="rId31" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{F663D9F1-08CC-5749-968A-7851DC6B334D}"/>
+    <hyperlink ref="I345" r:id="rId32" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{1DCCE41D-0A60-C547-AA00-799ECBCD2FA4}"/>
+    <hyperlink ref="I347" r:id="rId33" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{9EEB1B59-B5E1-5246-933C-27320078AEE1}"/>
+    <hyperlink ref="I348" r:id="rId34" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{F8763799-23B5-4146-A448-D1506A560F5B}"/>
+    <hyperlink ref="I350" r:id="rId35" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1142189" xr:uid="{0DA7D564-E6F8-BB42-96D7-1DDEC26EB7F8}"/>
+    <hyperlink ref="I354" r:id="rId36" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{FFBAA85D-5927-0644-95D8-4459806D9811}"/>
+    <hyperlink ref="I355" r:id="rId37" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{5708C9BA-98D6-0047-829A-6D81B7B4D9B0}"/>
+    <hyperlink ref="I356" r:id="rId38" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL2331468" xr:uid="{38212C86-332B-2D4F-914D-2D204BB598E0}"/>
+    <hyperlink ref="I357" r:id="rId39" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL2331468" xr:uid="{0D91B6EC-A02F-0D48-99E5-DAC51582DCA2}"/>
+    <hyperlink ref="I362" r:id="rId40" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{AA6B9E29-4208-4840-8A59-AF21218EABFD}"/>
+    <hyperlink ref="I364" r:id="rId41" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{CFAEEB80-7E3A-2F4D-B27F-0838846DB996}"/>
+    <hyperlink ref="I365" r:id="rId42" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{A2D4C8CA-E6F2-4B4F-A4F3-DB53EF714FE2}"/>
+    <hyperlink ref="I366" r:id="rId43" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{2FCC28DE-A74F-0642-ADCB-C44761CD046E}"/>
+    <hyperlink ref="I369" r:id="rId44" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{9C3B970D-D0FA-DE48-9CAC-494AE9565A2E}"/>
+    <hyperlink ref="I371" r:id="rId45" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL5126639" xr:uid="{5E1DCD8D-C70F-8D4C-AAD5-25ACF595052B}"/>
+    <hyperlink ref="I374" r:id="rId46" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{B1965716-BD98-364E-BD65-487D07D77973}"/>
+    <hyperlink ref="I376" r:id="rId47" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{F456591E-A05E-6646-9273-49AFC3D2A419}"/>
+    <hyperlink ref="I377" r:id="rId48" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{E55CB5BE-AD00-4A46-8A3F-DE98471A2BF6}"/>
+    <hyperlink ref="I379" r:id="rId49" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{A035627D-CE04-D94F-8E2C-5F00834EBFFE}"/>
+    <hyperlink ref="I380" r:id="rId50" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{D98FD7FA-4ADD-4448-931A-A13F9782A51A}"/>
+    <hyperlink ref="I382" r:id="rId51" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{4A37A8F9-88A8-BC44-9BCD-897B30A22E52}"/>
+    <hyperlink ref="I381" r:id="rId52" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{14283AA2-5FCF-4448-A1D6-5A19ADBD5F47}"/>
+    <hyperlink ref="I383" r:id="rId53" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{295E167C-BF95-1148-AB1E-DAAFBD3C5920}"/>
+    <hyperlink ref="I384" r:id="rId54" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{E7794773-D825-F049-86B7-CE1FC790B841}"/>
+    <hyperlink ref="I386" r:id="rId55" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1150789" xr:uid="{EAF6F8F3-BF61-F74E-B506-139FB7E6F864}"/>
+    <hyperlink ref="I388" r:id="rId56" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{3FE09900-81D1-6C40-A6C3-E8BEE166F4D9}"/>
+    <hyperlink ref="I393" r:id="rId57" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{B72801D8-F53E-4945-9D9C-D94552C78434}"/>
+    <hyperlink ref="I394" r:id="rId58" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{5A9F5449-1A48-E642-8944-A38E6BED13AF}"/>
+    <hyperlink ref="I395" r:id="rId59" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{EEA87C64-29CF-1C41-95D9-B0B60A1D6E44}"/>
+    <hyperlink ref="I396" r:id="rId60" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{7004252B-B169-CC4C-9976-D94705C3DC78}"/>
+    <hyperlink ref="I397" r:id="rId61" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{61E5BB24-3CC7-4C42-9CCA-C88BDCD36EA9}"/>
+    <hyperlink ref="I391" r:id="rId62" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4837227" xr:uid="{D4ED6F84-C6B6-CB4C-85E6-3D8A0053FA58}"/>
+    <hyperlink ref="I392" r:id="rId63" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671696" xr:uid="{0EBEEC98-F8D2-1541-9BF0-2E11E79074A8}"/>
+    <hyperlink ref="I399" r:id="rId64" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{AE92238E-D6C5-D540-B5EA-B653D643D0D9}"/>
+    <hyperlink ref="I400" r:id="rId65" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{9100A303-88F9-524E-99F9-B6B33AE3434B}"/>
+    <hyperlink ref="I402" r:id="rId66" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL3396969" xr:uid="{3637B675-39B4-A74F-97EA-F1124E43F56B}"/>
+    <hyperlink ref="I404" r:id="rId67" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{C5EB2FBC-F677-4048-A743-D907D7ED4DE8}"/>
+    <hyperlink ref="I403" r:id="rId68" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{A67E6A2C-B0D6-3F4D-A569-A2A59157377D}"/>
+    <hyperlink ref="I406" r:id="rId69" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL2331468" xr:uid="{78A9C280-A1C4-9A42-BE04-80AE94F5BFFE}"/>
+    <hyperlink ref="I408" r:id="rId70" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255275" xr:uid="{3997E592-AF8D-014F-B011-94477175E03B}"/>
+    <hyperlink ref="I416" r:id="rId71" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4257512" xr:uid="{6B6C4203-241E-BB4D-B0EA-BE4433D22B68}"/>
+    <hyperlink ref="I417" r:id="rId72" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL5126551" xr:uid="{E205C66B-FE91-744C-8B71-3A1698213773}"/>
+    <hyperlink ref="I420" r:id="rId73" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{3F361A3B-2DDB-D449-BB31-EA3F389FD422}"/>
+    <hyperlink ref="I423" r:id="rId74" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{0D9E7465-905E-974F-A77D-1919885ABE92}"/>
+    <hyperlink ref="I425" r:id="rId75" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL3351618" xr:uid="{22F1D2A8-3695-A047-8C92-985F272B47BD}"/>
+    <hyperlink ref="I428" r:id="rId76" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4190314" xr:uid="{EA21D424-813F-824B-8E9E-2DCD65C3DB2C}"/>
+    <hyperlink ref="I71" r:id="rId77" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1156683" xr:uid="{098C26B3-3BB2-D14F-A8B7-227BEA93B37A}"/>
+    <hyperlink ref="I30" r:id="rId78" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1156420" xr:uid="{7B186905-CF63-4D49-87D5-30F63528F7A6}"/>
+    <hyperlink ref="I172" r:id="rId79" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4706622" xr:uid="{1972A8CA-AB28-F541-AF4F-FF1D103563E9}"/>
+    <hyperlink ref="I189" r:id="rId80" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{67DD7D8E-29BB-6B41-B708-1578EF373020}"/>
+    <hyperlink ref="I188" r:id="rId81" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{0540BA7F-6858-0B4C-BAB0-9DD9E3853739}"/>
+    <hyperlink ref="I187" r:id="rId82" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671704" xr:uid="{A8E92FAF-6EFB-2A40-AA93-01AF3C1990FF}"/>
+    <hyperlink ref="I191" r:id="rId83" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{D67CB0AA-25E5-514F-B644-21EDD821BBD1}"/>
+    <hyperlink ref="I192" r:id="rId84" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{2F7688D5-D86C-704E-9FD6-017DC9C9D5F2}"/>
+    <hyperlink ref="I196" r:id="rId85" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{B37BB24E-B70F-5848-B861-A818F930BB02}"/>
+    <hyperlink ref="I195" r:id="rId86" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{6208CB76-A2D8-AF42-B6F5-DDBD26DCF5E8}"/>
+    <hyperlink ref="I194" r:id="rId87" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{AB987528-68B6-A14E-839C-40D4AD542C9A}"/>
+    <hyperlink ref="I193" r:id="rId88" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{181F1D5D-3B5F-6148-8415-4E2919C46A4C}"/>
+    <hyperlink ref="I198" r:id="rId89" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{91BF5D36-EA34-2A4C-89BA-CF4981324D64}"/>
+    <hyperlink ref="I200" r:id="rId90" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255275" xr:uid="{36E2A91C-B6EB-9047-968D-E7C175E128F4}"/>
+    <hyperlink ref="I201" r:id="rId91" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1142312" xr:uid="{39C8D12B-5BFA-1A47-8AF3-24B594666D96}"/>
+    <hyperlink ref="I203" r:id="rId92" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{55F6C0F4-59FD-194A-8F45-AB3D55B68AE7}"/>
+    <hyperlink ref="I205" r:id="rId93" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{31741F6A-BA32-314E-957E-107111237DAA}"/>
+    <hyperlink ref="I241" r:id="rId94" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL3396969" xr:uid="{1A51222E-0F97-0343-9CBE-4B6CEAC13D13}"/>
+    <hyperlink ref="I261" r:id="rId95" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{990CAD29-CB68-5C42-BB57-C47D96094A5E}"/>
+    <hyperlink ref="I284" r:id="rId96" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671726" xr:uid="{4E45E8E2-0DB8-5F45-9AA2-A2886A2E4D59}"/>
+    <hyperlink ref="I301" r:id="rId97" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4190314" xr:uid="{F46F4FED-60F1-1242-B4A2-088C905DF41E}"/>
+    <hyperlink ref="I304" r:id="rId98" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL5321250" xr:uid="{865140C8-07DC-6541-A046-3320A671020C}"/>
+    <hyperlink ref="I305" r:id="rId99" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4673175" xr:uid="{BD1EBED1-5502-9348-B71E-EC8CDD06DD10}"/>
+    <hyperlink ref="I306" r:id="rId100" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{D0669686-04C4-BF47-AB56-86996728C601}"/>
+    <hyperlink ref="I311" r:id="rId101" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL5352391" xr:uid="{60810FCA-1AC8-7840-BE74-67F985EBC44D}"/>
+    <hyperlink ref="I314" r:id="rId102" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{7BD95745-F163-6545-BE5A-2C6E9EFB68BE}"/>
+    <hyperlink ref="I319" r:id="rId103" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1629673" xr:uid="{366A2F8D-F6AF-0F4A-B371-6D71464906FB}"/>
+    <hyperlink ref="I321" r:id="rId104" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4007417" xr:uid="{8848E855-7F8A-AB48-8F56-DBFB7E91472B}"/>
+    <hyperlink ref="I331" r:id="rId105" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1649199" xr:uid="{24BCBE57-8D35-1C43-ACC2-78B0FA80427A}"/>
+    <hyperlink ref="I336" r:id="rId106" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4190314" xr:uid="{2A20B166-F4A3-1B46-89F7-0D5875B6AF8E}"/>
+    <hyperlink ref="I337" r:id="rId107" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL4190314" xr:uid="{11A043A8-CC67-FA4F-8F13-72CD4F8FCDFD}"/>
+    <hyperlink ref="I342" r:id="rId108" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1255382" xr:uid="{7C4EBA1F-194C-034F-8830-12194A50F1F5}"/>
+    <hyperlink ref="I346" r:id="rId109" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1649192" xr:uid="{23575900-4592-B047-A7D3-39DB7BAC461E}"/>
+    <hyperlink ref="I358" r:id="rId110" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1142472" xr:uid="{6C2D815C-2AD3-7843-B5E8-90561193FCE6}"/>
+    <hyperlink ref="I361" r:id="rId111" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1671696" xr:uid="{005F6736-204D-EF47-8E43-4ED1288E1268}"/>
+    <hyperlink ref="I412" r:id="rId112" display="https://www.ebi.ac.uk/chembl/explore/document/CHEMBL1649199" xr:uid="{B4AD8135-5F1E-BB49-A85B-CFA28FDE3098}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
